--- a/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,211 +656,223 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44835</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44744</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44653</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44555</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44464</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44373</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44282</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44191</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>637000</v>
+      </c>
+      <c r="E8" s="3">
         <v>530000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>454000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>458000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>565000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>450000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>460000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>394000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>356000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>326000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>327000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>377000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>334000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>231000</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>293000</v>
+      </c>
+      <c r="E9" s="3">
         <v>258000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>230000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>251000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>265000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>233000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>231000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>218000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>202000</v>
-      </c>
-      <c r="L9" s="3">
-        <v>173000</v>
       </c>
       <c r="M9" s="3">
         <v>173000</v>
       </c>
       <c r="N9" s="3">
+        <v>173000</v>
+      </c>
+      <c r="O9" s="3">
         <v>183000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>176000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>155000</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>344000</v>
+      </c>
+      <c r="E10" s="3">
         <v>272000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>224000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>207000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>300000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>217000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>229000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>176000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>154000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>153000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>154000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>194000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>158000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>76000</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -877,52 +889,56 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>225000</v>
+      </c>
+      <c r="E12" s="3">
         <v>218000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>211000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>235000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>224000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>206000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>179000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>180000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>154000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>132000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>128000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>130000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>128000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -965,8 +981,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1009,8 +1028,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1027,11 +1049,11 @@
         <v>17000</v>
       </c>
       <c r="H15" s="3">
+        <v>17000</v>
+      </c>
+      <c r="I15" s="3">
         <v>16000</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1041,8 +1063,8 @@
       <c r="L15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1053,8 +1075,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1068,96 +1093,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>564000</v>
+      </c>
+      <c r="E17" s="3">
         <v>522000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>487000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>539000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>541000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>475000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>450000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>440000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>400000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>346000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>342000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>355000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>345000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>308000</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E18" s="3">
         <v>8000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-33000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-81000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>24000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-25000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-46000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-44000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-20000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-15000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>22000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-77000</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1174,96 +1206,103 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>15000</v>
+        <v>11000</v>
       </c>
       <c r="E20" s="3">
         <v>15000</v>
       </c>
       <c r="F20" s="3">
+        <v>15000</v>
+      </c>
+      <c r="G20" s="3">
         <v>8000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>14000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2000</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>2000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>211000</v>
+      </c>
+      <c r="E21" s="3">
         <v>143000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>108000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>67000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>175000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>119000</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L21" s="3">
         <v>480000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N21" s="3">
         <v>237000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1273,18 +1312,18 @@
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="3">
         <v>4000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11000</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>16</v>
       </c>
@@ -1300,102 +1339,111 @@
       <c r="N22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E23" s="3">
         <v>23000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-18000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-73000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>34000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-30000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-44000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-46000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-20000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-15000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>24000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E24" s="3">
         <v>6000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4000</v>
-      </c>
-      <c r="H24" s="3">
-        <v>15000</v>
       </c>
       <c r="I24" s="3">
         <v>15000</v>
       </c>
       <c r="J24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="K24" s="3">
         <v>16000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7000</v>
-      </c>
-      <c r="L24" s="3">
-        <v>6000</v>
       </c>
       <c r="M24" s="3">
         <v>6000</v>
       </c>
       <c r="N24" s="3">
+        <v>6000</v>
+      </c>
+      <c r="O24" s="3">
         <v>-1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1438,96 +1486,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E26" s="3">
         <v>17000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-28000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-79000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>30000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-45000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-60000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-53000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-26000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-21000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>25000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E27" s="3">
         <v>17000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-28000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-79000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>30000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-45000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-60000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-53000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-26000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-21000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>25000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1570,8 +1627,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1614,8 +1674,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1658,8 +1721,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1702,96 +1768,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-15000</v>
+        <v>-11000</v>
       </c>
       <c r="E32" s="3">
         <v>-15000</v>
       </c>
       <c r="F32" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-8000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-14000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2000</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-2000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E33" s="3">
         <v>17000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-28000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-79000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>30000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-45000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-60000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-53000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-26000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-21000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>25000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1834,101 +1909,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E35" s="3">
         <v>17000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-28000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-79000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>30000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-45000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-60000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-53000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-26000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-21000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>25000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44835</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44744</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44653</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44555</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44464</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44373</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44282</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44191</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1945,8 +2029,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1963,32 +2048,33 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1212000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1193000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1142000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1161000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1024000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>871000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>774000</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2007,8 +2093,11 @@
       <c r="P41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2051,32 +2140,35 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>357000</v>
+      </c>
+      <c r="E43" s="3">
         <v>281000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>240000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>239000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>269000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1123000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1115000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2095,32 +2187,35 @@
       <c r="P43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>391000</v>
+      </c>
+      <c r="E44" s="3">
         <v>354000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>263000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>173000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>113000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>105000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>98000</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>16</v>
       </c>
@@ -2139,32 +2234,35 @@
       <c r="P44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>106000</v>
+      </c>
+      <c r="E45" s="3">
         <v>80000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>72000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>82000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>110000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>63000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>56000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2183,32 +2281,35 @@
       <c r="P45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2066000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1908000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1717000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1655000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1516000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2162000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2043000</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>16</v>
       </c>
@@ -2227,8 +2328,11 @@
       <c r="P46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2271,32 +2375,35 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>447000</v>
+      </c>
+      <c r="E48" s="3">
         <v>426000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>422000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>401000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>384000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>354000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>338000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>16</v>
       </c>
@@ -2315,32 +2422,35 @@
       <c r="P48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12948000</v>
+      </c>
+      <c r="E49" s="3">
         <v>13060000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13171000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13289000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13422000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13553000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13684000</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>16</v>
       </c>
@@ -2359,8 +2469,11 @@
       <c r="P49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2403,8 +2516,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2447,32 +2563,35 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E52" s="3">
         <v>111000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>120000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>117000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>119000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>95000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>97000</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>16</v>
       </c>
@@ -2491,8 +2610,11 @@
       <c r="P52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2535,32 +2657,35 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15577000</v>
+      </c>
+      <c r="E54" s="3">
         <v>15505000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15430000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15462000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15441000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16164000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16162000</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>16</v>
       </c>
@@ -2579,8 +2704,11 @@
       <c r="P54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2597,8 +2725,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2615,32 +2744,33 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>229000</v>
+      </c>
+      <c r="E57" s="3">
         <v>221000</v>
-      </c>
-      <c r="E57" s="3">
-        <v>208000</v>
       </c>
       <c r="F57" s="3">
         <v>208000</v>
       </c>
       <c r="G57" s="3">
+        <v>208000</v>
+      </c>
+      <c r="H57" s="3">
         <v>189000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>160000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>138000</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>16</v>
       </c>
@@ -2659,8 +2789,11 @@
       <c r="P57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2703,32 +2836,35 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>174000</v>
+      </c>
+      <c r="E59" s="3">
         <v>170000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>173000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>210000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>195000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4620000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4592000</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>16</v>
       </c>
@@ -2747,32 +2883,35 @@
       <c r="P59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>403000</v>
+      </c>
+      <c r="E60" s="3">
         <v>391000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>381000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>418000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>384000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4780000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4730000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>16</v>
       </c>
@@ -2791,8 +2930,11 @@
       <c r="P60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2835,32 +2977,35 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>250000</v>
+      </c>
+      <c r="E62" s="3">
         <v>241000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>249000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>257000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>263000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>224000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>233000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>16</v>
       </c>
@@ -2879,8 +3024,11 @@
       <c r="P62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2923,8 +3071,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2967,8 +3118,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3011,32 +3165,35 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>653000</v>
+      </c>
+      <c r="E66" s="3">
         <v>632000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>630000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>675000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>647000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5004000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4963000</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>16</v>
       </c>
@@ -3055,8 +3212,11 @@
       <c r="P66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3073,8 +3233,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3117,8 +3278,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3161,8 +3325,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3205,8 +3372,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3249,32 +3419,35 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-33000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-50000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-22000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>57000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11178000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11223000</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>16</v>
       </c>
@@ -3293,8 +3466,11 @@
       <c r="P72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3337,8 +3513,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3381,8 +3560,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3425,32 +3607,35 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14924000</v>
+      </c>
+      <c r="E76" s="3">
         <v>14873000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14800000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14787000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14794000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11160000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11199000</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>16</v>
       </c>
@@ -3469,8 +3654,11 @@
       <c r="P76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3513,101 +3701,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44835</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44744</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44653</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44555</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44464</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44373</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44282</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44191</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E81" s="3">
         <v>17000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-28000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-79000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>30000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-45000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-60000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-53000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-26000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-21000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>25000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3624,38 +3821,39 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E83" s="3">
         <v>120000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>126000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>140000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>137000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>138000</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L83" s="3">
         <v>526000</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>16</v>
       </c>
@@ -3668,8 +3866,11 @@
       <c r="P83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3712,8 +3913,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3756,8 +3960,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3800,8 +4007,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3844,8 +4054,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3888,38 +4101,41 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E89" s="3">
         <v>88000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>26000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>171000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>151000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>162000</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L89" s="3">
         <v>599000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>16</v>
       </c>
@@ -3932,8 +4148,11 @@
       <c r="P89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3950,40 +4169,41 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-32000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-26000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-32000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-26000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-53000</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>16</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>16</v>
@@ -3994,8 +4214,11 @@
       <c r="P91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4038,8 +4261,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4082,38 +4308,41 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-32000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-26000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>868000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-25000</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L94" s="3">
         <v>-157000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>16</v>
       </c>
@@ -4126,8 +4355,11 @@
       <c r="P94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4144,8 +4376,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4188,8 +4421,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4232,8 +4468,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4276,8 +4515,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4320,38 +4562,41 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-17000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-9000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-866000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-36000</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L100" s="3">
         <v>91000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>16</v>
       </c>
@@ -4364,38 +4609,41 @@
       <c r="P100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4000</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-3000</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>16</v>
       </c>
@@ -4408,38 +4656,41 @@
       <c r="P101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E102" s="3">
         <v>50000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-16000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>138000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>153000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>98000</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K102" s="3">
+      <c r="K102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L102" s="3">
         <v>532000</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>16</v>
       </c>
@@ -4450,6 +4701,9 @@
         <v>16</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
   <si>
     <t>MBLY</t>
   </si>
@@ -656,223 +656,236 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
         <v>45290</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44835</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44744</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44653</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44555</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44464</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44373</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44282</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44191</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>239000</v>
+      </c>
+      <c r="E8" s="3">
         <v>637000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>530000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>454000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>458000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>565000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>450000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>460000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>394000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>356000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>326000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>327000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>377000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>334000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>231000</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>185000</v>
+      </c>
+      <c r="E9" s="3">
         <v>293000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>258000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>230000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>251000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>265000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>233000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>231000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>218000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>202000</v>
-      </c>
-      <c r="M9" s="3">
-        <v>173000</v>
       </c>
       <c r="N9" s="3">
         <v>173000</v>
       </c>
       <c r="O9" s="3">
+        <v>173000</v>
+      </c>
+      <c r="P9" s="3">
         <v>183000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>176000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>155000</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E10" s="3">
         <v>344000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>272000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>224000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>207000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>300000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>217000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>229000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>176000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>154000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>153000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>154000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>194000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>158000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>76000</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -890,55 +903,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>243000</v>
+      </c>
+      <c r="E12" s="3">
         <v>225000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>218000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>211000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>235000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>224000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>206000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>179000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>180000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>154000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>132000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>128000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>130000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>128000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -984,8 +1001,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1031,8 +1051,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1052,11 +1075,11 @@
         <v>17000</v>
       </c>
       <c r="I15" s="3">
+        <v>17000</v>
+      </c>
+      <c r="J15" s="3">
         <v>16000</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1066,8 +1089,8 @@
       <c r="M15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1078,8 +1101,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1094,102 +1120,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>477000</v>
+      </c>
+      <c r="E17" s="3">
         <v>564000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>522000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>487000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>539000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>541000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>475000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>450000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>440000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>400000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>346000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>342000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>355000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>345000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>308000</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-238000</v>
+      </c>
+      <c r="E18" s="3">
         <v>73000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>8000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-33000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-81000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>24000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-25000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-46000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-44000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-20000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-15000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>22000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-77000</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1207,107 +1240,114 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E20" s="3">
         <v>11000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>15000</v>
       </c>
       <c r="F20" s="3">
         <v>15000</v>
       </c>
       <c r="G20" s="3">
+        <v>15000</v>
+      </c>
+      <c r="H20" s="3">
         <v>8000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>14000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2000</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>2000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-96000</v>
+      </c>
+      <c r="E21" s="3">
         <v>211000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>143000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>108000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>67000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>175000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>119000</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M21" s="3">
         <v>480000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O21" s="3">
         <v>237000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -1315,18 +1355,18 @@
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="3">
         <v>4000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11000</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>16</v>
       </c>
@@ -1342,108 +1382,117 @@
       <c r="O22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-221000</v>
+      </c>
+      <c r="E23" s="3">
         <v>84000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>23000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-18000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-73000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>34000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-30000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-44000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-46000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-20000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-15000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>24000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E24" s="3">
         <v>21000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4000</v>
-      </c>
-      <c r="I24" s="3">
-        <v>15000</v>
       </c>
       <c r="J24" s="3">
         <v>15000</v>
       </c>
       <c r="K24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L24" s="3">
         <v>16000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7000</v>
-      </c>
-      <c r="M24" s="3">
-        <v>6000</v>
       </c>
       <c r="N24" s="3">
         <v>6000</v>
       </c>
       <c r="O24" s="3">
+        <v>6000</v>
+      </c>
+      <c r="P24" s="3">
         <v>-1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1489,102 +1538,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-218000</v>
+      </c>
+      <c r="E26" s="3">
         <v>63000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>17000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-28000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-79000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>30000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-45000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-60000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-53000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-26000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-21000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>25000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-218000</v>
+      </c>
+      <c r="E27" s="3">
         <v>63000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>17000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-28000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-79000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>30000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-45000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-60000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-53000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-26000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-21000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>25000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1630,8 +1688,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1677,8 +1738,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1724,8 +1788,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1771,102 +1838,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-11000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-15000</v>
       </c>
       <c r="F32" s="3">
         <v>-15000</v>
       </c>
       <c r="G32" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="H32" s="3">
         <v>-8000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-14000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2000</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-2000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-218000</v>
+      </c>
+      <c r="E33" s="3">
         <v>63000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>17000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-28000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-79000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>30000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-45000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-60000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-53000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-26000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-21000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>25000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1912,107 +1988,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-218000</v>
+      </c>
+      <c r="E35" s="3">
         <v>63000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>17000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-28000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-79000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>30000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-45000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-60000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-53000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-26000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-21000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>25000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
         <v>45290</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44835</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44744</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44653</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44555</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44464</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44373</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44282</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44191</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2030,8 +2115,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2049,35 +2135,36 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1223000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1212000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1193000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1142000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1161000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1024000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>871000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>774000</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2096,8 +2183,11 @@
       <c r="Q41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2143,35 +2233,38 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E43" s="3">
         <v>357000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>281000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>240000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>239000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>269000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1123000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1115000</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2190,35 +2283,38 @@
       <c r="Q43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>456000</v>
+      </c>
+      <c r="E44" s="3">
         <v>391000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>354000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>263000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>173000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>113000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>105000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>98000</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>16</v>
       </c>
@@ -2237,35 +2333,38 @@
       <c r="Q44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E45" s="3">
         <v>106000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>80000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>72000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>82000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>110000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>63000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>56000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2284,35 +2383,38 @@
       <c r="Q45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1931000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2066000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1908000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1717000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1655000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1516000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2162000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2043000</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>16</v>
       </c>
@@ -2331,8 +2433,11 @@
       <c r="Q46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2378,35 +2483,38 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>454000</v>
+      </c>
+      <c r="E48" s="3">
         <v>447000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>426000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>422000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>401000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>384000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>354000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>338000</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>16</v>
       </c>
@@ -2425,35 +2533,38 @@
       <c r="Q48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12837000</v>
+      </c>
+      <c r="E49" s="3">
         <v>12948000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13060000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13171000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13289000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13422000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13553000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13684000</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>16</v>
       </c>
@@ -2472,8 +2583,11 @@
       <c r="Q49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2519,8 +2633,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2566,35 +2683,38 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E52" s="3">
         <v>116000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>111000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>120000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>117000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>119000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>95000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>97000</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>16</v>
       </c>
@@ -2613,8 +2733,11 @@
       <c r="Q52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2660,35 +2783,38 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15342000</v>
+      </c>
+      <c r="E54" s="3">
         <v>15577000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15505000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15430000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15462000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15441000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16164000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16162000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>16</v>
       </c>
@@ -2707,8 +2833,11 @@
       <c r="Q54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2726,8 +2855,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2745,35 +2875,36 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E57" s="3">
         <v>229000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>221000</v>
-      </c>
-      <c r="F57" s="3">
-        <v>208000</v>
       </c>
       <c r="G57" s="3">
         <v>208000</v>
       </c>
       <c r="H57" s="3">
+        <v>208000</v>
+      </c>
+      <c r="I57" s="3">
         <v>189000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>160000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>138000</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>16</v>
       </c>
@@ -2792,8 +2923,11 @@
       <c r="Q57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2839,35 +2973,38 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>163000</v>
+      </c>
+      <c r="E59" s="3">
         <v>174000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>170000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>173000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>210000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>195000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4620000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4592000</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>16</v>
       </c>
@@ -2886,35 +3023,38 @@
       <c r="Q59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>329000</v>
+      </c>
+      <c r="E60" s="3">
         <v>403000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>391000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>381000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>418000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>384000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4780000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4730000</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>16</v>
       </c>
@@ -2933,8 +3073,11 @@
       <c r="Q60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2980,8 +3123,11 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2989,26 +3135,26 @@
         <v>250000</v>
       </c>
       <c r="E62" s="3">
+        <v>250000</v>
+      </c>
+      <c r="F62" s="3">
         <v>241000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>249000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>257000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>263000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>224000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>233000</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>16</v>
       </c>
@@ -3027,8 +3173,11 @@
       <c r="Q62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3074,8 +3223,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3121,8 +3273,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3168,35 +3323,38 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>579000</v>
+      </c>
+      <c r="E66" s="3">
         <v>653000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>632000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>630000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>675000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>647000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5004000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4963000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>16</v>
       </c>
@@ -3215,8 +3373,11 @@
       <c r="Q66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3234,8 +3395,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3281,8 +3443,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3328,8 +3493,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3375,8 +3543,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3422,35 +3593,38 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-188000</v>
+      </c>
+      <c r="E72" s="3">
         <v>30000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-33000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-50000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-22000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>57000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11178000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11223000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>16</v>
       </c>
@@ -3469,8 +3643,11 @@
       <c r="Q72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3516,8 +3693,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3563,8 +3743,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3610,35 +3793,38 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14763000</v>
+      </c>
+      <c r="E76" s="3">
         <v>14924000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14873000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14800000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14787000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14794000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11160000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11199000</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>16</v>
       </c>
@@ -3657,8 +3843,11 @@
       <c r="Q76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3704,107 +3893,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
         <v>45290</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44835</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44744</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44653</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44555</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44464</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44373</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44282</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44191</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-218000</v>
+      </c>
+      <c r="E81" s="3">
         <v>63000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>17000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-28000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-79000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>30000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-45000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-60000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-53000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-26000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-21000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>25000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3822,41 +4020,42 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E83" s="3">
         <v>127000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>120000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>126000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>140000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>137000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>138000</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M83" s="3">
         <v>526000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>16</v>
       </c>
@@ -3869,8 +4068,11 @@
       <c r="Q83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3916,8 +4118,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3963,8 +4168,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4010,8 +4218,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4057,8 +4268,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4104,41 +4318,44 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E89" s="3">
         <v>109000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>88000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>26000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>171000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>151000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>162000</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M89" s="3">
         <v>599000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>16</v>
       </c>
@@ -4151,8 +4368,11 @@
       <c r="Q89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4170,43 +4390,44 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-23000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-32000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-26000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-32000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-26000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-53000</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>16</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>16</v>
@@ -4217,8 +4438,11 @@
       <c r="Q91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4264,8 +4488,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4311,41 +4538,44 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-32000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-26000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>868000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-25000</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M94" s="3">
         <v>-157000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>16</v>
       </c>
@@ -4358,8 +4588,11 @@
       <c r="Q94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4377,8 +4610,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4424,8 +4658,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4471,8 +4708,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4518,8 +4758,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4565,41 +4808,44 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-71000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-17000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-9000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-866000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-36000</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M100" s="3">
         <v>91000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>16</v>
       </c>
@@ -4612,41 +4858,44 @@
       <c r="Q100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4000</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-3000</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M101" s="3">
         <v>-1000</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>16</v>
       </c>
@@ -4659,41 +4908,44 @@
       <c r="Q101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E102" s="3">
         <v>19000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>50000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-16000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>138000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>153000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>98000</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L102" s="3">
+      <c r="L102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M102" s="3">
         <v>532000</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>16</v>
       </c>
@@ -4704,6 +4956,9 @@
         <v>16</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
   <si>
     <t>MBLY</t>
   </si>
@@ -656,236 +656,249 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45290</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44835</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44744</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44653</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44555</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44464</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44373</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44282</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44191</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>439000</v>
+      </c>
+      <c r="E8" s="3">
         <v>239000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>637000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>530000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>454000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>458000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>565000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>450000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>460000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>394000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>356000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>326000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>327000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>377000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>334000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>231000</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>230000</v>
+      </c>
+      <c r="E9" s="3">
         <v>185000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>293000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>258000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>230000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>251000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>265000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>233000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>231000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>218000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>202000</v>
-      </c>
-      <c r="N9" s="3">
-        <v>173000</v>
       </c>
       <c r="O9" s="3">
         <v>173000</v>
       </c>
       <c r="P9" s="3">
+        <v>173000</v>
+      </c>
+      <c r="Q9" s="3">
         <v>183000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>176000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>155000</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>209000</v>
+      </c>
+      <c r="E10" s="3">
         <v>54000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>344000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>272000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>224000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>207000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>300000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>217000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>229000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>176000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>154000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>153000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>154000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>194000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>158000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>76000</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -904,58 +917,62 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>256000</v>
+      </c>
+      <c r="E12" s="3">
         <v>243000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>225000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>218000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>211000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>235000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>224000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>206000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>179000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>180000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>154000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>132000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>128000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>130000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>128000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1004,8 +1021,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1054,8 +1074,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1078,11 +1101,11 @@
         <v>17000</v>
       </c>
       <c r="J15" s="3">
+        <v>17000</v>
+      </c>
+      <c r="K15" s="3">
         <v>16000</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1092,8 +1115,8 @@
       <c r="N15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1104,8 +1127,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1121,108 +1147,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>533000</v>
+      </c>
+      <c r="E17" s="3">
         <v>477000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>564000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>522000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>487000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>539000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>541000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>475000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>450000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>440000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>400000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>346000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>342000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>355000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>345000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>308000</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-94000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-238000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>73000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-33000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-81000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>24000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-25000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-46000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-44000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-20000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-15000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>22000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-11000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-77000</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1241,116 +1274,123 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E20" s="3">
         <v>17000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>11000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>15000</v>
       </c>
       <c r="G20" s="3">
         <v>15000</v>
       </c>
       <c r="H20" s="3">
+        <v>15000</v>
+      </c>
+      <c r="I20" s="3">
         <v>8000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>14000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2000</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>2000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-96000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>211000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>143000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>108000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>67000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>175000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>119000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N21" s="3">
         <v>480000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P21" s="3">
         <v>237000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1358,18 +1398,18 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="3">
         <v>4000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11000</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>16</v>
       </c>
@@ -1385,114 +1425,123 @@
       <c r="P22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-81000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-221000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>84000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>23000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-18000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-73000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>34000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-30000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-44000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-46000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-20000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-15000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>24000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-16000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>21000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>10000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>15000</v>
       </c>
       <c r="K24" s="3">
         <v>15000</v>
       </c>
       <c r="L24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="M24" s="3">
         <v>16000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7000</v>
-      </c>
-      <c r="N24" s="3">
-        <v>6000</v>
       </c>
       <c r="O24" s="3">
         <v>6000</v>
       </c>
       <c r="P24" s="3">
+        <v>6000</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1541,108 +1590,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-86000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-218000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>63000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>17000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-28000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-79000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>30000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-45000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-60000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-53000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-26000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-21000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>25000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-14000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-86000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-218000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>63000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>17000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-28000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-79000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>30000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-45000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-60000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-53000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-26000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-21000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>25000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-14000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,8 +1749,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1741,8 +1802,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1855,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1841,108 +1908,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-17000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-11000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-15000</v>
       </c>
       <c r="G32" s="3">
         <v>-15000</v>
       </c>
       <c r="H32" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-8000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-14000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2000</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-86000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-218000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>63000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>17000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-28000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-79000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>30000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-45000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-60000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-53000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-26000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-21000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>25000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-14000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1991,113 +2067,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-86000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-218000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>63000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>17000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-28000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-79000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>30000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-45000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-60000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-53000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-26000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-21000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>25000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-14000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45290</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44835</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44744</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44653</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44555</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44464</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44373</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44282</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44191</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2116,8 +2201,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2136,38 +2222,39 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1203000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1223000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1212000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1193000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1142000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1161000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1024000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>871000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>774000</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2186,8 +2273,11 @@
       <c r="R41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2236,38 +2326,41 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E43" s="3">
         <v>120000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>357000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>281000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>240000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>239000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>269000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1123000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1115000</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2286,38 +2379,41 @@
       <c r="R43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>485000</v>
+      </c>
+      <c r="E44" s="3">
         <v>456000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>391000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>354000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>263000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>173000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>113000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>105000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>98000</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>16</v>
       </c>
@@ -2336,38 +2432,41 @@
       <c r="R44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E45" s="3">
         <v>132000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>106000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>80000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>72000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>82000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>110000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>63000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>56000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2386,38 +2485,41 @@
       <c r="R45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2007000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1931000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2066000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1908000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1717000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1655000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1516000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2162000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2043000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>16</v>
       </c>
@@ -2436,8 +2538,11 @@
       <c r="R46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2486,38 +2591,41 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>456000</v>
+      </c>
+      <c r="E48" s="3">
         <v>454000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>447000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>426000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>422000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>401000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>384000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>354000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>338000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>16</v>
       </c>
@@ -2536,38 +2644,41 @@
       <c r="R48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12726000</v>
+      </c>
+      <c r="E49" s="3">
         <v>12837000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12948000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13060000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13171000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13289000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13422000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13553000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13684000</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>16</v>
       </c>
@@ -2586,8 +2697,11 @@
       <c r="R49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2636,8 +2750,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2686,38 +2803,41 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E52" s="3">
         <v>120000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>116000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>111000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>120000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>117000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>119000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>95000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>97000</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>16</v>
       </c>
@@ -2736,8 +2856,11 @@
       <c r="R52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2786,38 +2909,41 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15307000</v>
+      </c>
+      <c r="E54" s="3">
         <v>15342000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15577000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15505000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15430000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15462000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15441000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16164000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16162000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>16</v>
       </c>
@@ -2836,8 +2962,11 @@
       <c r="R54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2856,8 +2985,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,38 +3006,39 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>171000</v>
+      </c>
+      <c r="E57" s="3">
         <v>166000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>229000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>221000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>208000</v>
       </c>
       <c r="H57" s="3">
         <v>208000</v>
       </c>
       <c r="I57" s="3">
+        <v>208000</v>
+      </c>
+      <c r="J57" s="3">
         <v>189000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>160000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>138000</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>16</v>
       </c>
@@ -2926,8 +3057,11 @@
       <c r="R57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2976,38 +3110,41 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E59" s="3">
         <v>163000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>174000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>170000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>173000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>210000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>195000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4620000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4592000</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3026,38 +3163,41 @@
       <c r="R59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>346000</v>
+      </c>
+      <c r="E60" s="3">
         <v>329000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>403000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>391000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>381000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>418000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>384000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4780000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4730000</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3076,8 +3216,11 @@
       <c r="R60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3126,38 +3269,41 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>250000</v>
+        <v>242000</v>
       </c>
       <c r="E62" s="3">
         <v>250000</v>
       </c>
       <c r="F62" s="3">
+        <v>250000</v>
+      </c>
+      <c r="G62" s="3">
         <v>241000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>249000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>257000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>263000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>224000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>233000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>16</v>
       </c>
@@ -3176,8 +3322,11 @@
       <c r="R62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3226,8 +3375,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3276,8 +3428,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3326,38 +3481,41 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>588000</v>
+      </c>
+      <c r="E66" s="3">
         <v>579000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>653000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>632000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>630000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>675000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>647000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5004000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4963000</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>16</v>
       </c>
@@ -3376,8 +3534,11 @@
       <c r="R66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3396,8 +3557,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3446,8 +3608,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3496,8 +3661,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3546,8 +3714,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3596,38 +3767,41 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-274000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-188000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>30000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-33000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-50000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-22000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>57000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11178000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11223000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>16</v>
       </c>
@@ -3646,8 +3820,11 @@
       <c r="R72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3696,8 +3873,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3746,8 +3926,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3796,38 +3979,41 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14719000</v>
+      </c>
+      <c r="E76" s="3">
         <v>14763000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14924000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14873000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14800000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14787000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14794000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11160000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11199000</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>16</v>
       </c>
@@ -3846,8 +4032,11 @@
       <c r="R76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3896,113 +4085,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45290</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44835</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44744</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44653</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44555</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44464</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44373</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44282</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44191</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-86000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-218000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>63000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>17000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-28000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-79000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>30000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-45000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-60000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-53000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-26000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-21000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>25000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-14000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4021,44 +4219,45 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E83" s="3">
         <v>125000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>127000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>120000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>126000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>140000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>137000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>138000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N83" s="3">
         <v>526000</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>16</v>
       </c>
@@ -4071,8 +4270,11 @@
       <c r="R83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4121,8 +4323,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4171,8 +4376,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4221,8 +4429,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4271,8 +4482,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4321,44 +4535,47 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E89" s="3">
         <v>40000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>109000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>88000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>26000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>171000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>151000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>162000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N89" s="3">
         <v>599000</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>16</v>
       </c>
@@ -4371,8 +4588,11 @@
       <c r="R89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4391,46 +4611,47 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-22000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-23000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-17000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-32000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-26000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-32000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-26000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-53000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>16</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>16</v>
@@ -4441,8 +4662,11 @@
       <c r="R91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4491,8 +4715,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4541,44 +4768,47 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-22000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-23000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-17000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-32000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-26000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>868000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-25000</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N94" s="3">
         <v>-157000</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>16</v>
       </c>
@@ -4591,8 +4821,11 @@
       <c r="R94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4611,8 +4844,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4661,8 +4895,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4711,8 +4948,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4761,8 +5001,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4811,44 +5054,47 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-71000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-17000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-866000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-36000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N100" s="3">
         <v>91000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>16</v>
       </c>
@@ -4861,44 +5107,47 @@
       <c r="R100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4000</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>16</v>
       </c>
@@ -4911,44 +5160,47 @@
       <c r="R101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E102" s="3">
         <v>12000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>19000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>50000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-16000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>138000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>153000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>98000</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N102" s="3">
         <v>532000</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>16</v>
       </c>
@@ -4959,6 +5211,9 @@
         <v>16</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="92">
   <si>
     <t>MBLY</t>
   </si>
@@ -656,249 +656,262 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45290</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44835</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44744</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44653</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44555</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44464</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44373</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44282</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44191</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>486000</v>
+      </c>
+      <c r="E8" s="3">
         <v>439000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>239000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>637000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>530000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>454000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>458000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>565000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>450000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>460000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>394000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>356000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>326000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>327000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>377000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>334000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>231000</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>249000</v>
+      </c>
+      <c r="E9" s="3">
         <v>230000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>185000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>293000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>258000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>230000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>251000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>265000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>233000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>231000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>218000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>202000</v>
-      </c>
-      <c r="O9" s="3">
-        <v>173000</v>
       </c>
       <c r="P9" s="3">
         <v>173000</v>
       </c>
       <c r="Q9" s="3">
+        <v>173000</v>
+      </c>
+      <c r="R9" s="3">
         <v>183000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>176000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>155000</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>237000</v>
+      </c>
+      <c r="E10" s="3">
         <v>209000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>54000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>344000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>272000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>224000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>207000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>300000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>217000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>229000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>176000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>154000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>153000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>154000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>194000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>158000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>76000</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -918,61 +931,65 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>298400</v>
+      </c>
+      <c r="E12" s="3">
         <v>256000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>243000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>225000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>218000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>211000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>235000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>224000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>206000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>179000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>180000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>154000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>132000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>128000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>130000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>128000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1024,31 +1041,34 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>2698600</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1077,38 +1097,41 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>33000</v>
+      </c>
+      <c r="F15" s="3">
+        <v>31000</v>
+      </c>
+      <c r="G15" s="3">
+        <v>32000</v>
+      </c>
+      <c r="H15" s="3">
+        <v>26000</v>
+      </c>
+      <c r="I15" s="3">
+        <v>25000</v>
+      </c>
+      <c r="J15" s="3">
+        <v>24000</v>
+      </c>
+      <c r="K15" s="3">
         <v>17000</v>
       </c>
-      <c r="E15" s="3">
-        <v>17000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>17000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>17000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>17000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>17000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>17000</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>16000</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1118,8 +1141,8 @@
       <c r="O15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1130,8 +1153,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,114 +1174,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>593400</v>
+      </c>
+      <c r="E17" s="3">
         <v>533000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>477000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>564000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>522000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>487000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>539000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>541000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>475000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>450000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>440000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>400000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>346000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>342000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>355000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>345000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>308000</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-107400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-94000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-238000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>73000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-33000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-81000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>24000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-25000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-46000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-44000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-20000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>22000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-11000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-77000</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1275,114 +1308,121 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>13000</v>
+        <v>-13000</v>
       </c>
       <c r="E20" s="3">
-        <v>17000</v>
+        <v>-13000</v>
       </c>
       <c r="F20" s="3">
-        <v>11000</v>
+        <v>-17000</v>
       </c>
       <c r="G20" s="3">
-        <v>15000</v>
+        <v>-11000</v>
       </c>
       <c r="H20" s="3">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="I20" s="3">
-        <v>8000</v>
+        <v>-15000</v>
       </c>
       <c r="J20" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="K20" s="3">
         <v>14000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2000</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>2000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>46000</v>
+        <v>-61400</v>
       </c>
       <c r="E21" s="3">
-        <v>-96000</v>
+        <v>-48000</v>
       </c>
       <c r="F21" s="3">
-        <v>211000</v>
+        <v>-190000</v>
       </c>
       <c r="G21" s="3">
-        <v>143000</v>
+        <v>116000</v>
       </c>
       <c r="H21" s="3">
-        <v>108000</v>
+        <v>49000</v>
       </c>
       <c r="I21" s="3">
-        <v>67000</v>
+        <v>7000</v>
       </c>
       <c r="J21" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="K21" s="3">
         <v>175000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>119000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O21" s="3">
         <v>480000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q21" s="3">
         <v>237000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1392,27 +1432,27 @@
       <c r="E22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" s="3">
         <v>4000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11000</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>16</v>
       </c>
@@ -1428,120 +1468,129 @@
       <c r="Q22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2793000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-81000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-221000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>84000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>23000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-18000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-73000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>34000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-30000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-44000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-46000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-20000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>24000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-16000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-78000</v>
+      </c>
+      <c r="E24" s="3">
         <v>5000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>21000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>10000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4000</v>
-      </c>
-      <c r="K24" s="3">
-        <v>15000</v>
       </c>
       <c r="L24" s="3">
         <v>15000</v>
       </c>
       <c r="M24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="N24" s="3">
         <v>16000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7000</v>
-      </c>
-      <c r="O24" s="3">
-        <v>6000</v>
       </c>
       <c r="P24" s="3">
         <v>6000</v>
       </c>
       <c r="Q24" s="3">
+        <v>6000</v>
+      </c>
+      <c r="R24" s="3">
         <v>-1000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,114 +1642,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2715000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-86000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-218000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>63000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>17000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-28000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-79000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>30000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-45000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-60000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-53000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-26000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>25000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-14000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2715000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-86000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-218000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>63000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>17000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-28000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-79000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>30000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-45000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-60000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-53000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-26000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>25000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-14000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1810,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1805,8 +1866,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1922,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,114 +1978,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-13000</v>
+        <v>13000</v>
       </c>
       <c r="E32" s="3">
-        <v>-17000</v>
+        <v>13000</v>
       </c>
       <c r="F32" s="3">
-        <v>-11000</v>
+        <v>17000</v>
       </c>
       <c r="G32" s="3">
-        <v>-15000</v>
+        <v>11000</v>
       </c>
       <c r="H32" s="3">
-        <v>-15000</v>
+        <v>15000</v>
       </c>
       <c r="I32" s="3">
-        <v>-8000</v>
+        <v>15000</v>
       </c>
       <c r="J32" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-14000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2000</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-2000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2715000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-86000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-218000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>63000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>17000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-28000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-79000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>30000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-45000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-60000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-53000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-26000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>25000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-14000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,119 +2146,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2715000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-86000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-218000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>63000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>17000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-28000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-79000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>30000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-45000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-60000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-53000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-26000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>25000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-14000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45290</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44835</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44744</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44653</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44555</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44464</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44373</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44282</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44191</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2287,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,41 +2309,42 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1293000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1203000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1223000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1212000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1193000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1142000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1161000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1024000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>871000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>774000</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2276,13 +2363,16 @@
       <c r="S41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -2329,41 +2419,44 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>223000</v>
+      </c>
+      <c r="E43" s="3">
         <v>204000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>120000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>357000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>281000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>240000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>239000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>269000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1123000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1115000</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2382,41 +2475,44 @@
       <c r="S43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>457000</v>
+      </c>
+      <c r="E44" s="3">
         <v>485000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>456000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>391000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>354000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>263000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>173000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>113000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>105000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>98000</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>16</v>
       </c>
@@ -2435,41 +2531,44 @@
       <c r="S44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E45" s="3">
         <v>115000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>132000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>106000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>80000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>72000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>82000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>110000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>63000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>56000</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2488,41 +2587,44 @@
       <c r="S45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2099000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2007000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1931000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2066000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1908000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1717000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1655000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1516000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2162000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2043000</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>16</v>
       </c>
@@ -2541,31 +2643,34 @@
       <c r="S46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2594,41 +2699,44 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>461000</v>
+      </c>
+      <c r="E48" s="3">
         <v>456000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>454000</v>
       </c>
-      <c r="F48" s="3">
-        <v>447000</v>
-      </c>
       <c r="G48" s="3">
+        <v>496000</v>
+      </c>
+      <c r="H48" s="3">
         <v>426000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>422000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>401000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>384000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>354000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>338000</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>16</v>
       </c>
@@ -2647,41 +2755,44 @@
       <c r="S48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9920000</v>
+      </c>
+      <c r="E49" s="3">
         <v>12726000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12837000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12948000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13060000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13171000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13289000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13422000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13553000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13684000</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>16</v>
       </c>
@@ -2700,8 +2811,11 @@
       <c r="S49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2867,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,41 +2923,44 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>123000</v>
+      </c>
+      <c r="E52" s="3">
         <v>118000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>120000</v>
       </c>
-      <c r="F52" s="3">
-        <v>116000</v>
-      </c>
       <c r="G52" s="3">
+        <v>67000</v>
+      </c>
+      <c r="H52" s="3">
         <v>111000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>120000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>117000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>119000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>95000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>97000</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>16</v>
       </c>
@@ -2859,8 +2979,11 @@
       <c r="S52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,41 +3035,44 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12603000</v>
+      </c>
+      <c r="E54" s="3">
         <v>15307000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15342000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15577000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15505000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15430000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15462000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15441000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16164000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16162000</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>16</v>
       </c>
@@ -2965,8 +3091,11 @@
       <c r="S54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3115,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,41 +3137,42 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E57" s="3">
         <v>171000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>166000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>229000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>221000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>208000</v>
       </c>
       <c r="I57" s="3">
         <v>208000</v>
       </c>
       <c r="J57" s="3">
+        <v>208000</v>
+      </c>
+      <c r="K57" s="3">
         <v>189000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>160000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>138000</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3060,22 +3191,25 @@
       <c r="S57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -3113,41 +3247,44 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>175000</v>
+        <v>52000</v>
       </c>
       <c r="E59" s="3">
-        <v>163000</v>
+        <v>82000</v>
       </c>
       <c r="F59" s="3">
-        <v>174000</v>
+        <v>31000</v>
       </c>
       <c r="G59" s="3">
-        <v>170000</v>
+        <v>38000</v>
       </c>
       <c r="H59" s="3">
-        <v>173000</v>
+        <v>91000</v>
       </c>
       <c r="I59" s="3">
-        <v>210000</v>
+        <v>86000</v>
       </c>
       <c r="J59" s="3">
+        <v>116000</v>
+      </c>
+      <c r="K59" s="3">
         <v>195000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4620000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4592000</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3166,41 +3303,44 @@
       <c r="S59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>362000</v>
+      </c>
+      <c r="E60" s="3">
         <v>346000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>329000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>403000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>391000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>381000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>418000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>384000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4780000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4730000</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3219,31 +3359,34 @@
       <c r="S60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>51000</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>51000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>39000</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>39000</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3272,41 +3415,44 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>242000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>250000</v>
-      </c>
-      <c r="F62" s="3">
-        <v>250000</v>
+      <c r="D62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G62" s="3">
-        <v>241000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>249000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>257000</v>
-      </c>
-      <c r="J62" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K62" s="3">
         <v>263000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>224000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>233000</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>16</v>
       </c>
@@ -3325,8 +3471,11 @@
       <c r="S62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3527,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3583,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,41 +3639,44 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>525000</v>
+      </c>
+      <c r="E66" s="3">
         <v>588000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>579000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>653000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>632000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>630000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>675000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>647000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5004000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4963000</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>16</v>
       </c>
@@ -3537,8 +3695,11 @@
       <c r="S66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3719,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3773,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3829,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3717,8 +3885,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,41 +3941,44 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2989000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-274000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-188000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>30000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-33000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-50000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-22000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>57000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11178000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>11223000</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>16</v>
       </c>
@@ -3823,8 +3997,11 @@
       <c r="S72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4053,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4109,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,41 +4165,44 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12078000</v>
+      </c>
+      <c r="E76" s="3">
         <v>14719000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14763000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14924000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14873000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14800000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14787000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14794000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11160000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11199000</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4035,8 +4221,11 @@
       <c r="S76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,119 +4277,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45290</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44835</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44744</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44653</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44555</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44464</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44373</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44282</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44191</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2715000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-86000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-218000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>63000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>17000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-28000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-79000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>30000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-45000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-60000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-53000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-26000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>25000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-14000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,47 +4418,48 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>127000</v>
+        <v>9000</v>
       </c>
       <c r="E83" s="3">
-        <v>125000</v>
+        <v>8000</v>
       </c>
       <c r="F83" s="3">
-        <v>127000</v>
+        <v>7000</v>
       </c>
       <c r="G83" s="3">
-        <v>120000</v>
+        <v>6000</v>
       </c>
       <c r="H83" s="3">
-        <v>126000</v>
+        <v>7000</v>
       </c>
       <c r="I83" s="3">
-        <v>140000</v>
+        <v>5000</v>
       </c>
       <c r="J83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K83" s="3">
         <v>137000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>138000</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O83" s="3">
         <v>526000</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>16</v>
       </c>
@@ -4273,8 +4472,11 @@
       <c r="S83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4528,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4584,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4640,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4696,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,47 +4752,50 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>126000</v>
+      </c>
+      <c r="E89" s="3">
         <v>30000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>40000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>109000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>88000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>26000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>171000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>151000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>162000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O89" s="3">
         <v>599000</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>16</v>
       </c>
@@ -4591,8 +4808,11 @@
       <c r="S89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,49 +4832,50 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-24000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-22000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-23000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-17000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-32000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-26000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-32000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-53000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>16</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>16</v>
@@ -4665,8 +4886,11 @@
       <c r="S91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +4942,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,47 +4998,50 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-42000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-22000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-23000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-32000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-26000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>868000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-25000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O94" s="3">
         <v>-157000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>16</v>
       </c>
@@ -4824,8 +5054,11 @@
       <c r="S94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,31 +5078,32 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4898,8 +5132,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5188,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5244,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,47 +5300,50 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-71000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-17000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-866000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-36000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O100" s="3">
         <v>91000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>16</v>
       </c>
@@ -5110,47 +5356,50 @@
       <c r="S100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-3000</v>
       </c>
-      <c r="E101" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>4000</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="I101" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>16</v>
       </c>
@@ -5163,47 +5412,50 @@
       <c r="S101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-22000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>19000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>50000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-16000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>138000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>153000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>98000</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O102" s="3">
         <v>532000</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>16</v>
       </c>
@@ -5214,6 +5466,9 @@
         <v>16</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
   <si>
     <t>MBLY</t>
   </si>
@@ -656,150 +656,156 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E7" s="2">
         <v>45563</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45472</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45381</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45290</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45108</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45017</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44835</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44744</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44653</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44555</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44464</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44373</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44282</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44191</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>490000</v>
+      </c>
+      <c r="E8" s="3">
         <v>486000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>439000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>239000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>637000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>530000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>454000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>458000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>565000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>450000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>460000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>394000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>356000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>326000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>327000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>377000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>334000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>231000</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -807,111 +813,117 @@
         <v>249000</v>
       </c>
       <c r="E9" s="3">
+        <v>249000</v>
+      </c>
+      <c r="F9" s="3">
         <v>230000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>185000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>293000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>258000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>230000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>251000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>265000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>233000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>231000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>218000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>202000</v>
-      </c>
-      <c r="P9" s="3">
-        <v>173000</v>
       </c>
       <c r="Q9" s="3">
         <v>173000</v>
       </c>
       <c r="R9" s="3">
+        <v>173000</v>
+      </c>
+      <c r="S9" s="3">
         <v>183000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>176000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>155000</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>241000</v>
+      </c>
+      <c r="E10" s="3">
         <v>237000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>209000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>54000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>344000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>272000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>224000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>207000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>300000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>217000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>229000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>176000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>154000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>153000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>154000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>194000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>158000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>76000</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -932,64 +944,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>276400</v>
+      </c>
+      <c r="E12" s="3">
         <v>298400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>256000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>243000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>225000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>218000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>211000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>235000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>224000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>206000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>179000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>180000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>154000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>132000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>128000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>130000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>128000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1044,17 +1060,20 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E14" s="3">
         <v>2698600</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1070,8 +1089,8 @@
       <c r="J14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1100,8 +1119,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1112,29 +1134,29 @@
         <v>33000</v>
       </c>
       <c r="F15" s="3">
+        <v>33000</v>
+      </c>
+      <c r="G15" s="3">
         <v>31000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>32000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>26000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>25000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>24000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>17000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>16000</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1144,8 +1166,8 @@
       <c r="P15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1156,8 +1178,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1175,120 +1200,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>571400</v>
+      </c>
+      <c r="E17" s="3">
         <v>593400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>533000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>477000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>564000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>522000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>487000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>539000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>541000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>475000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>450000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>440000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>400000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>346000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>342000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>355000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>345000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>308000</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-81400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-107400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-94000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-238000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>73000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-33000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-81000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>24000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-25000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-46000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-44000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-15000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>22000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-11000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-77000</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1309,120 +1341,127 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-13000</v>
+        <v>-18000</v>
       </c>
       <c r="E20" s="3">
         <v>-13000</v>
       </c>
       <c r="F20" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="G20" s="3">
         <v>-17000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-11000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-15000</v>
       </c>
       <c r="I20" s="3">
         <v>-15000</v>
       </c>
       <c r="J20" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="K20" s="3">
         <v>-8000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>14000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2000</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>2000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-61400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-48000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-190000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>116000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>49000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-49000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>175000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>119000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P21" s="3">
         <v>480000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R21" s="3">
         <v>237000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1447,15 +1486,15 @@
       <c r="J22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L22" s="3">
         <v>4000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>11000</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>16</v>
       </c>
@@ -1471,126 +1510,135 @@
       <c r="R22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-68000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2793000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-81000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-221000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>84000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>23000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-18000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-73000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>34000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-30000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-44000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-46000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-15000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>24000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-16000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-78000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-3000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>21000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>10000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4000</v>
-      </c>
-      <c r="L24" s="3">
-        <v>15000</v>
       </c>
       <c r="M24" s="3">
         <v>15000</v>
       </c>
       <c r="N24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="O24" s="3">
         <v>16000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7000</v>
-      </c>
-      <c r="P24" s="3">
-        <v>6000</v>
       </c>
       <c r="Q24" s="3">
         <v>6000</v>
       </c>
       <c r="R24" s="3">
+        <v>6000</v>
+      </c>
+      <c r="S24" s="3">
         <v>-1000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1645,120 +1693,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2715000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-86000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-218000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>63000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>17000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-28000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-79000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>30000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-45000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-60000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-53000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-21000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>25000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-14000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2715000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-86000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-218000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>63000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>17000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-28000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-79000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>30000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-45000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-60000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-53000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-21000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>25000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-14000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1813,8 +1870,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1869,8 +1929,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1925,8 +1988,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1981,120 +2047,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>13000</v>
+        <v>18000</v>
       </c>
       <c r="E32" s="3">
         <v>13000</v>
       </c>
       <c r="F32" s="3">
+        <v>13000</v>
+      </c>
+      <c r="G32" s="3">
         <v>17000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>11000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>15000</v>
       </c>
       <c r="I32" s="3">
         <v>15000</v>
       </c>
       <c r="J32" s="3">
+        <v>15000</v>
+      </c>
+      <c r="K32" s="3">
         <v>8000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-14000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2000</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-2000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2715000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-86000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-218000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>63000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>17000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-28000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-79000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>30000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-45000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-60000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-53000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-21000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>25000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-14000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2149,125 +2224,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2715000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-86000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-218000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>63000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>17000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-28000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-79000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>30000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-45000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-60000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-53000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-21000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>25000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-14000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E38" s="2">
         <v>45563</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45472</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45381</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45290</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45108</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45017</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44835</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44744</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44653</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44555</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44464</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44373</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44282</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44191</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2288,8 +2372,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2310,44 +2395,45 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1426000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1293000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1203000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1223000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1212000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1193000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1142000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1161000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1024000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>871000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>774000</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2366,17 +2452,20 @@
       <c r="T41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>10000</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -2422,44 +2511,47 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>212000</v>
+      </c>
+      <c r="E43" s="3">
         <v>223000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>204000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>120000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>357000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>281000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>240000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>239000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>269000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1123000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1115000</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2478,44 +2570,47 @@
       <c r="T43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>415000</v>
+      </c>
+      <c r="E44" s="3">
         <v>457000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>485000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>456000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>391000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>354000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>263000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>173000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>113000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>105000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>98000</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>16</v>
       </c>
@@ -2534,44 +2629,47 @@
       <c r="T44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E45" s="3">
         <v>116000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>115000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>132000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>106000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>80000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>72000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>82000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>110000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>63000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>56000</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2590,44 +2688,47 @@
       <c r="T45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2174000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2099000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2007000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1931000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2066000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1908000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1717000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1655000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1516000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2162000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2043000</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>16</v>
       </c>
@@ -2646,8 +2747,11 @@
       <c r="T46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2672,8 +2776,8 @@
       <c r="J47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2702,44 +2806,47 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>505000</v>
+      </c>
+      <c r="E48" s="3">
         <v>461000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>456000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>454000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>496000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>426000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>422000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>401000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>384000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>354000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>338000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>16</v>
       </c>
@@ -2758,44 +2865,47 @@
       <c r="T48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9809000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9920000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12726000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12837000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12948000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13060000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13171000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13289000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13422000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13553000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13684000</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>16</v>
       </c>
@@ -2814,8 +2924,11 @@
       <c r="T49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2870,8 +2983,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2926,44 +3042,47 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E52" s="3">
         <v>123000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>118000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>120000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>67000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>111000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>120000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>117000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>119000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>95000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>97000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>16</v>
       </c>
@@ -2982,8 +3101,11 @@
       <c r="T52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3038,44 +3160,47 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12579000</v>
+      </c>
+      <c r="E54" s="3">
         <v>12603000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15307000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15342000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15577000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15505000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15430000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15462000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15441000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16164000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16162000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3094,8 +3219,11 @@
       <c r="T54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3116,8 +3244,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3138,44 +3267,45 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>190000</v>
+      </c>
+      <c r="E57" s="3">
         <v>166000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>171000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>166000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>229000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>221000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>208000</v>
       </c>
       <c r="J57" s="3">
         <v>208000</v>
       </c>
       <c r="K57" s="3">
+        <v>208000</v>
+      </c>
+      <c r="L57" s="3">
         <v>189000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>160000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>138000</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3194,26 +3324,29 @@
       <c r="T57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="E58" s="3">
         <v>2000</v>
       </c>
       <c r="F58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G58" s="3">
         <v>4000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12000</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -3250,44 +3383,47 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E59" s="3">
         <v>52000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>82000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>31000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>38000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>91000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>86000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>116000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>195000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4620000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4592000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3306,44 +3442,47 @@
       <c r="T59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>333000</v>
+      </c>
+      <c r="E60" s="3">
         <v>362000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>346000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>329000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>403000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>391000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>381000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>418000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>384000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4780000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4730000</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3362,35 +3501,38 @@
       <c r="T60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E61" s="3">
         <v>51000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>50000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>51000</v>
-      </c>
-      <c r="G61" s="3">
-        <v>39000</v>
       </c>
       <c r="H61" s="3">
         <v>39000</v>
       </c>
       <c r="I61" s="3">
+        <v>39000</v>
+      </c>
+      <c r="J61" s="3">
         <v>42000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>44000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3418,13 +3560,16 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>16</v>
+      <c r="D62" s="3">
+        <v>13000</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>16</v>
@@ -3432,30 +3577,30 @@
       <c r="F62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" s="3">
         <v>7000</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>16</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L62" s="3">
         <v>263000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>224000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>233000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>16</v>
       </c>
@@ -3474,8 +3619,11 @@
       <c r="T62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3530,8 +3678,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3586,8 +3737,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3642,44 +3796,47 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>492000</v>
+      </c>
+      <c r="E66" s="3">
         <v>525000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>588000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>579000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>653000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>632000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>630000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>675000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>647000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5004000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4963000</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>16</v>
       </c>
@@ -3698,8 +3855,11 @@
       <c r="T66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3720,8 +3880,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3776,8 +3937,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3832,8 +3996,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3888,8 +4055,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3944,44 +4114,47 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3060000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2989000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-274000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-188000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>30000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-33000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-50000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-22000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>57000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>11178000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11223000</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4000,8 +4173,11 @@
       <c r="T72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4056,8 +4232,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4112,8 +4291,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4168,44 +4350,47 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12087000</v>
+      </c>
+      <c r="E76" s="3">
         <v>12078000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14719000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14763000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14924000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14873000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14800000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14787000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14794000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11160000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11199000</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4224,8 +4409,11 @@
       <c r="T76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4280,125 +4468,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E80" s="2">
         <v>45563</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45472</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45381</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45290</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45108</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45017</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44835</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44744</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44653</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44555</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44464</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44373</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44282</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44191</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2715000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-86000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-218000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>63000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>17000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-28000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-79000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>30000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-45000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-60000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-53000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-21000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>25000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-14000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4419,50 +4616,51 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E83" s="3">
         <v>9000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>5000</v>
       </c>
       <c r="J83" s="3">
         <v>5000</v>
       </c>
       <c r="K83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L83" s="3">
         <v>137000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>138000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P83" s="3">
         <v>526000</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>16</v>
       </c>
@@ -4475,8 +4673,11 @@
       <c r="T83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4531,8 +4732,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4587,8 +4791,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4643,8 +4850,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4699,8 +4909,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4755,50 +4968,53 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E89" s="3">
         <v>126000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>30000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>40000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>109000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>88000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>26000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>171000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>151000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>162000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P89" s="3">
         <v>599000</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>16</v>
       </c>
@@ -4811,8 +5027,11 @@
       <c r="T89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4833,52 +5052,53 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-22000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-24000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-22000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-23000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-32000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-26000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-32000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-26000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-53000</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>16</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>16</v>
@@ -4889,8 +5109,11 @@
       <c r="T91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4945,8 +5168,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5001,50 +5227,53 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-34000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-42000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-22000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-23000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-32000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-26000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>868000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-25000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P94" s="3">
         <v>-157000</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5057,8 +5286,11 @@
       <c r="T94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5079,8 +5311,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5105,8 +5338,8 @@
       <c r="J96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5135,8 +5368,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5191,8 +5427,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5247,8 +5486,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5303,50 +5545,53 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-50000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-71000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-17000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-866000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-36000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P100" s="3">
         <v>91000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>16</v>
       </c>
@@ -5359,50 +5604,53 @@
       <c r="T100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4000</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="I101" s="3">
         <v>-3000</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="J101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-3000</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>16</v>
       </c>
@@ -5415,50 +5663,53 @@
       <c r="T101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E102" s="3">
         <v>90000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-22000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>19000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>50000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-16000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>138000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>153000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>98000</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P102" s="3">
         <v>532000</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>16</v>
       </c>
@@ -5469,6 +5720,9 @@
         <v>16</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
   <si>
     <t>MBLY</t>
   </si>
@@ -656,274 +656,287 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
         <v>45654</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45563</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45472</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45381</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45290</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45108</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45017</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44835</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44744</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44653</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44555</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44464</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44373</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44282</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44191</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>438000</v>
+      </c>
+      <c r="E8" s="3">
         <v>490000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>486000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>439000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>239000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>637000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>530000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>454000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>458000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>565000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>450000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>460000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>394000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>356000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>326000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>327000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>377000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>334000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>231000</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>249000</v>
+        <v>231000</v>
       </c>
       <c r="E9" s="3">
         <v>249000</v>
       </c>
       <c r="F9" s="3">
+        <v>249000</v>
+      </c>
+      <c r="G9" s="3">
         <v>230000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>185000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>293000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>258000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>230000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>251000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>265000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>233000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>231000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>218000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>202000</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>173000</v>
       </c>
       <c r="R9" s="3">
         <v>173000</v>
       </c>
       <c r="S9" s="3">
+        <v>173000</v>
+      </c>
+      <c r="T9" s="3">
         <v>183000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>176000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>155000</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>207000</v>
+      </c>
+      <c r="E10" s="3">
         <v>241000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>237000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>209000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>54000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>344000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>272000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>224000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>207000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>300000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>217000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>229000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>176000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>154000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>153000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>154000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>194000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>158000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>76000</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -945,67 +958,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>275000</v>
+      </c>
+      <c r="E12" s="3">
         <v>276400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>298400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>256000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>243000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>225000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>218000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>211000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>235000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>224000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>206000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>179000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>180000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>154000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>132000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>128000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>130000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>128000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1063,20 +1080,23 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="3">
         <v>4600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2698600</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1092,8 +1112,8 @@
       <c r="K14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1122,13 +1142,16 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>33000</v>
+        <v>35000</v>
       </c>
       <c r="E15" s="3">
         <v>33000</v>
@@ -1137,29 +1160,29 @@
         <v>33000</v>
       </c>
       <c r="G15" s="3">
+        <v>33000</v>
+      </c>
+      <c r="H15" s="3">
         <v>31000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>32000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>26000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>25000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>24000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>17000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>16000</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1169,8 +1192,8 @@
       <c r="Q15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1181,8 +1204,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,126 +1227,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>555000</v>
+      </c>
+      <c r="E17" s="3">
         <v>571400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>593400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>533000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>477000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>564000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>522000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>487000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>539000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>541000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>475000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>450000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>440000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>400000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>346000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>342000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>355000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>345000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>308000</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-117000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-81400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-107400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-94000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-238000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>73000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>8000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-33000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-81000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>24000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-25000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-46000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-44000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-20000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-15000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>22000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-11000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-77000</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1342,126 +1375,133 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="3">
         <v>-18000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-13000</v>
       </c>
       <c r="F20" s="3">
         <v>-13000</v>
       </c>
       <c r="G20" s="3">
-        <v>-17000</v>
-      </c>
-      <c r="H20" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="3">
         <v>-11000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-15000</v>
       </c>
       <c r="J20" s="3">
         <v>-15000</v>
       </c>
       <c r="K20" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="L20" s="3">
         <v>-8000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>14000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>2000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-82000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-30400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-61400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-48000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-190000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-207000</v>
+      </c>
+      <c r="I21" s="3">
         <v>116000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>49000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-49000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>175000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>119000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q21" s="3">
         <v>480000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S21" s="3">
         <v>237000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1489,15 +1529,15 @@
       <c r="K22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M22" s="3">
         <v>4000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>11000</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>16</v>
       </c>
@@ -1513,73 +1553,79 @@
       <c r="S22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-99000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-68000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2793000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-81000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-221000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>84000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>23000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-18000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-73000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>34000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-30000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-44000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-46000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-20000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-15000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>24000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-16000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1587,58 +1633,61 @@
         <v>3000</v>
       </c>
       <c r="E24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F24" s="3">
         <v>-78000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-3000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>21000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>10000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4000</v>
-      </c>
-      <c r="M24" s="3">
-        <v>15000</v>
       </c>
       <c r="N24" s="3">
         <v>15000</v>
       </c>
       <c r="O24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="P24" s="3">
         <v>16000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7000</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>6000</v>
       </c>
       <c r="R24" s="3">
         <v>6000</v>
       </c>
       <c r="S24" s="3">
+        <v>6000</v>
+      </c>
+      <c r="T24" s="3">
         <v>-1000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-2000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,126 +1745,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-102000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-71000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2715000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-86000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-218000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>63000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>17000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-28000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-79000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>30000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-45000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-60000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-53000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-26000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-21000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>25000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-14000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-102000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-71000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2715000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-86000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-218000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>63000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>17000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-28000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-79000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>30000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-45000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-60000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-53000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-26000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-21000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>25000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-14000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,8 +1931,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1932,8 +1993,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2055,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,126 +2117,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="3">
         <v>18000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>13000</v>
       </c>
       <c r="F32" s="3">
         <v>13000</v>
       </c>
       <c r="G32" s="3">
-        <v>17000</v>
-      </c>
-      <c r="H32" s="3">
+        <v>13000</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="3">
         <v>11000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>15000</v>
       </c>
       <c r="J32" s="3">
         <v>15000</v>
       </c>
       <c r="K32" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L32" s="3">
         <v>8000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-14000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2000</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-2000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-102000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-71000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2715000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-86000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-218000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>63000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>17000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-28000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-79000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>30000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-45000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-60000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-53000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-26000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-21000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>25000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-14000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,131 +2303,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-102000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-71000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2715000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-86000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-218000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>63000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>17000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-28000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-79000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>30000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-45000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-60000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-53000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-26000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-21000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>25000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-14000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
         <v>45654</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45563</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45472</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45381</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45290</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45108</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45017</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44835</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44744</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44653</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44555</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44464</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44373</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44282</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44191</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2458,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,47 +2482,48 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1512000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1426000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1293000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1203000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1223000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1212000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1193000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1142000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1161000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1024000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>871000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>774000</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2455,20 +2542,23 @@
       <c r="U41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>10000</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -2514,47 +2604,50 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E43" s="3">
         <v>212000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>223000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>204000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>120000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>357000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>281000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>240000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>239000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>269000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1123000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1115000</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2573,47 +2666,50 @@
       <c r="U43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E44" s="3">
         <v>415000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>457000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>485000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>456000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>391000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>354000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>263000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>173000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>113000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>105000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>98000</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>16</v>
       </c>
@@ -2632,47 +2728,50 @@
       <c r="U44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E45" s="3">
         <v>121000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>116000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>115000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>132000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>106000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>80000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>72000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>82000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>110000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>63000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>56000</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2691,47 +2790,50 @@
       <c r="U45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2215000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2174000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2099000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2007000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1931000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2066000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1908000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1717000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1655000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1516000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2162000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2043000</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>16</v>
       </c>
@@ -2750,13 +2852,16 @@
       <c r="U46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>16</v>
+      <c r="D47" s="3">
+        <v>10000</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>16</v>
@@ -2779,8 +2884,8 @@
       <c r="K47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2809,47 +2914,50 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>450000</v>
+      </c>
+      <c r="E48" s="3">
         <v>505000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>461000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>456000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>454000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>496000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>426000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>422000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>401000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>384000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>354000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>338000</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>16</v>
       </c>
@@ -2868,47 +2976,50 @@
       <c r="U48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9698000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9809000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9920000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12726000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12837000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12948000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13060000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13171000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13289000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13422000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13553000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13684000</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>16</v>
       </c>
@@ -2927,8 +3038,11 @@
       <c r="U49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3100,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,47 +3162,50 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E52" s="3">
         <v>91000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>123000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>118000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>120000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>67000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>111000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>120000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>117000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>119000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>95000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>97000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3104,8 +3224,11 @@
       <c r="U52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,47 +3286,50 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12498000</v>
+      </c>
+      <c r="E54" s="3">
         <v>12579000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12603000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15307000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15342000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15577000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15505000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15430000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15462000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15441000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16164000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16162000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3222,8 +3348,11 @@
       <c r="U54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3374,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,47 +3398,48 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E57" s="3">
         <v>190000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>166000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>171000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>166000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>229000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>221000</v>
-      </c>
-      <c r="J57" s="3">
-        <v>208000</v>
       </c>
       <c r="K57" s="3">
         <v>208000</v>
       </c>
       <c r="L57" s="3">
+        <v>208000</v>
+      </c>
+      <c r="M57" s="3">
         <v>189000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>160000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>138000</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3327,29 +3458,32 @@
       <c r="U57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>13000</v>
-      </c>
-      <c r="E58" s="3">
-        <v>2000</v>
       </c>
       <c r="F58" s="3">
         <v>2000</v>
       </c>
       <c r="G58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H58" s="3">
         <v>4000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -3386,47 +3520,50 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E59" s="3">
         <v>22000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>52000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>82000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>31000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>38000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>91000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>86000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>116000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>195000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4620000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4592000</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3445,47 +3582,50 @@
       <c r="U59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>290000</v>
+      </c>
+      <c r="E60" s="3">
         <v>333000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>362000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>346000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>329000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>403000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>391000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>381000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>418000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>384000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4780000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4730000</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3504,38 +3644,41 @@
       <c r="U60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>37000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>51000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>50000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>51000</v>
-      </c>
-      <c r="H61" s="3">
-        <v>39000</v>
       </c>
       <c r="I61" s="3">
         <v>39000</v>
       </c>
       <c r="J61" s="3">
+        <v>39000</v>
+      </c>
+      <c r="K61" s="3">
         <v>42000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>44000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3563,47 +3706,50 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E62" s="3">
         <v>13000</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F62" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" s="3">
         <v>7000</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>16</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M62" s="3">
         <v>263000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>224000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>233000</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>16</v>
       </c>
@@ -3622,8 +3768,11 @@
       <c r="U62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +3830,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +3892,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,47 +3954,50 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>449000</v>
+      </c>
+      <c r="E66" s="3">
         <v>492000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>525000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>588000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>579000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>653000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>632000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>630000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>675000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>647000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5004000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4963000</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>16</v>
       </c>
@@ -3858,8 +4016,11 @@
       <c r="U66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4042,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4102,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4164,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4058,8 +4226,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,47 +4288,50 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3162000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3060000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2989000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-274000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-188000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>30000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-33000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-50000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-22000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>57000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11178000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11223000</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4176,8 +4350,11 @@
       <c r="U72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4412,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +4474,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,47 +4536,50 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12049000</v>
+      </c>
+      <c r="E76" s="3">
         <v>12087000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12078000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14719000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14763000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14924000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14873000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14800000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14787000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14794000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11160000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11199000</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4412,8 +4598,11 @@
       <c r="U76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,131 +4660,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
         <v>45654</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45563</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45472</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45381</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45290</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45108</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45017</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44835</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44744</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44653</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44555</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44464</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44373</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44282</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44191</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-102000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-71000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2715000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-86000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-218000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>63000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>17000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-28000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-79000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>30000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-45000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-60000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-53000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-26000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-21000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>25000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-14000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,53 +4815,54 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E83" s="3">
         <v>15000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>9000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>5000</v>
       </c>
       <c r="K83" s="3">
         <v>5000</v>
       </c>
       <c r="L83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="M83" s="3">
         <v>137000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>138000</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q83" s="3">
         <v>526000</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>16</v>
       </c>
@@ -4676,8 +4875,11 @@
       <c r="U83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +4937,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +4999,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5061,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5123,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,53 +5185,56 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E89" s="3">
         <v>204000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>126000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>30000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>40000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>109000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>88000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>26000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>171000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>151000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>162000</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q89" s="3">
         <v>599000</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5030,8 +5247,11 @@
       <c r="U89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,55 +5273,56 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-22000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-24000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-22000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-23000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-17000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-32000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-32000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-26000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-53000</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>16</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>16</v>
@@ -5112,8 +5333,11 @@
       <c r="U91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +5395,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,53 +5457,56 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-22000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-34000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-42000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-22000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-23000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-17000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-32000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-26000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>868000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-25000</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-157000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5289,8 +5519,11 @@
       <c r="U94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,8 +5545,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5341,8 +5575,8 @@
       <c r="K96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5371,8 +5605,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +5667,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +5729,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,53 +5791,56 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-50000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-71000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-17000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-866000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-36000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q100" s="3">
         <v>91000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>16</v>
       </c>
@@ -5607,53 +5853,56 @@
       <c r="U100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4000</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="J101" s="3">
         <v>-3000</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-3000</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>16</v>
       </c>
@@ -5666,53 +5915,56 @@
       <c r="U101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>89000</v>
+      </c>
+      <c r="E102" s="3">
         <v>132000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>90000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-22000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>19000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>50000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-16000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>138000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>153000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>98000</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q102" s="3">
         <v>532000</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>16</v>
       </c>
@@ -5723,6 +5975,9 @@
         <v>16</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
@@ -656,287 +656,300 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45654</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45472</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45381</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45290</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45108</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45017</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44835</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44744</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44653</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44555</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44464</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44373</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44282</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44191</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>506000</v>
+      </c>
+      <c r="E8" s="3">
         <v>438000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>490000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>486000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>439000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>239000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>637000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>530000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>454000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>458000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>565000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>450000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>460000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>394000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>356000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>326000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>327000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>377000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>334000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>231000</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>254000</v>
+      </c>
+      <c r="E9" s="3">
         <v>231000</v>
-      </c>
-      <c r="E9" s="3">
-        <v>249000</v>
       </c>
       <c r="F9" s="3">
         <v>249000</v>
       </c>
       <c r="G9" s="3">
+        <v>249000</v>
+      </c>
+      <c r="H9" s="3">
         <v>230000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>185000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>293000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>258000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>230000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>251000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>265000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>233000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>231000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>218000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>202000</v>
-      </c>
-      <c r="R9" s="3">
-        <v>173000</v>
       </c>
       <c r="S9" s="3">
         <v>173000</v>
       </c>
       <c r="T9" s="3">
+        <v>173000</v>
+      </c>
+      <c r="U9" s="3">
         <v>183000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>176000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>155000</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>252000</v>
+      </c>
+      <c r="E10" s="3">
         <v>207000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>241000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>237000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>209000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>54000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>344000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>272000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>224000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>207000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>300000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>217000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>229000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>176000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>154000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>153000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>154000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>194000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>158000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>76000</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -959,70 +972,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E12" s="3">
         <v>275000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>276400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>298400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>256000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>243000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>225000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>218000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>211000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>235000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>224000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>206000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>179000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>180000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>154000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>132000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>128000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>130000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>128000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1083,23 +1100,26 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3">
         <v>4600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2698600</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1115,8 +1135,8 @@
       <c r="L14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1145,8 +1165,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1154,7 +1177,7 @@
         <v>35000</v>
       </c>
       <c r="E15" s="3">
-        <v>33000</v>
+        <v>35000</v>
       </c>
       <c r="F15" s="3">
         <v>33000</v>
@@ -1163,29 +1186,29 @@
         <v>33000</v>
       </c>
       <c r="H15" s="3">
+        <v>33000</v>
+      </c>
+      <c r="I15" s="3">
         <v>31000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>32000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>26000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>25000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>24000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>17000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>16000</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1195,8 +1218,8 @@
       <c r="R15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1207,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,132 +1254,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>580000</v>
+      </c>
+      <c r="E17" s="3">
         <v>555000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>571400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>593400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>533000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>477000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>564000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>522000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>487000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>539000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>541000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>475000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>450000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>440000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>400000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>346000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>342000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>355000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>345000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>308000</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-117000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-81400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-107400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-94000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-238000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>73000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>8000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-33000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-81000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>24000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-25000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-46000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-44000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-20000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-15000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>22000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-11000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-77000</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1376,132 +1409,139 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>16</v>
+      <c r="D20" s="3">
+        <v>-13000</v>
       </c>
       <c r="E20" s="3">
         <v>-18000</v>
       </c>
       <c r="F20" s="3">
-        <v>-13000</v>
+        <v>-18000</v>
       </c>
       <c r="G20" s="3">
         <v>-13000</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>16</v>
+      <c r="H20" s="3">
+        <v>-13000</v>
       </c>
       <c r="I20" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-11000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-15000</v>
       </c>
       <c r="K20" s="3">
         <v>-15000</v>
       </c>
       <c r="L20" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="M20" s="3">
         <v>-8000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>14000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>6000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2000</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>2000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-82000</v>
+        <v>-26000</v>
       </c>
       <c r="E21" s="3">
+        <v>-64000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-30400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-61400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-48000</v>
       </c>
-      <c r="H21" s="3">
-        <v>-207000</v>
-      </c>
       <c r="I21" s="3">
+        <v>-190000</v>
+      </c>
+      <c r="J21" s="3">
         <v>116000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>49000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-49000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>175000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>119000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R21" s="3">
         <v>480000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T21" s="3">
         <v>237000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1532,15 +1572,15 @@
       <c r="L22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N22" s="3">
         <v>4000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11000</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>16</v>
       </c>
@@ -1556,138 +1596,147 @@
       <c r="T22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-61000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-99000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-68000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2793000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-81000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-221000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>84000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>23000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-18000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-73000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>34000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-30000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-44000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-46000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-20000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-15000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>24000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-16000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="E24" s="3">
         <v>3000</v>
       </c>
       <c r="F24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G24" s="3">
         <v>-78000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-3000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>21000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>10000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4000</v>
-      </c>
-      <c r="N24" s="3">
-        <v>15000</v>
       </c>
       <c r="O24" s="3">
         <v>15000</v>
       </c>
       <c r="P24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="Q24" s="3">
         <v>16000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7000</v>
-      </c>
-      <c r="R24" s="3">
-        <v>6000</v>
       </c>
       <c r="S24" s="3">
         <v>6000</v>
       </c>
       <c r="T24" s="3">
+        <v>6000</v>
+      </c>
+      <c r="U24" s="3">
         <v>-1000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-2000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,132 +1797,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-102000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-71000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2715000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-86000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-218000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>63000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>17000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-28000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-79000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>30000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-45000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-60000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-53000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-26000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-21000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>25000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-14000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-102000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-71000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2715000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-86000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-218000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>63000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>17000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-28000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-79000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>30000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-45000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-60000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-53000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-26000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-21000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>25000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-14000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,132 +2187,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>16</v>
+      <c r="D32" s="3">
+        <v>13000</v>
       </c>
       <c r="E32" s="3">
         <v>18000</v>
       </c>
       <c r="F32" s="3">
-        <v>13000</v>
+        <v>18000</v>
       </c>
       <c r="G32" s="3">
         <v>13000</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>16</v>
+      <c r="H32" s="3">
+        <v>13000</v>
       </c>
       <c r="I32" s="3">
+        <v>17000</v>
+      </c>
+      <c r="J32" s="3">
         <v>11000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>15000</v>
       </c>
       <c r="K32" s="3">
         <v>15000</v>
       </c>
       <c r="L32" s="3">
+        <v>15000</v>
+      </c>
+      <c r="M32" s="3">
         <v>8000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-14000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-6000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2000</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-2000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-102000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-71000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2715000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-86000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-218000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>63000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-28000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-79000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>30000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-45000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-60000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-53000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-26000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-21000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>25000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-14000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,137 +2382,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-102000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-71000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2715000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-86000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-218000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>63000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-28000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-79000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>30000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-45000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-60000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-53000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-26000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-21000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>25000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-14000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45654</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45472</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45381</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45290</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45108</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45017</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44835</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44744</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44653</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44555</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44464</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44373</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44282</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44191</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,50 +2569,51 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1709000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1512000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1426000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1293000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1203000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1223000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1212000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1193000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1142000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1161000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1024000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>871000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>774000</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2545,23 +2632,26 @@
       <c r="V41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>44000</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>10000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -2607,8 +2697,11 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2616,41 +2709,41 @@
         <v>217000</v>
       </c>
       <c r="E43" s="3">
+        <v>217000</v>
+      </c>
+      <c r="F43" s="3">
         <v>212000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>223000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>204000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>120000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>357000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>281000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>240000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>239000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>269000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1123000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1115000</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2669,50 +2762,53 @@
       <c r="V43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>325000</v>
+      </c>
+      <c r="E44" s="3">
         <v>364000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>415000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>457000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>485000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>456000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>391000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>354000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>263000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>173000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>113000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>105000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>98000</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>16</v>
       </c>
@@ -2731,50 +2827,53 @@
       <c r="V44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>146000</v>
+      </c>
+      <c r="E45" s="3">
         <v>78000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>121000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>116000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>115000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>132000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>106000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>80000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>72000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>82000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>110000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>63000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>56000</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2793,50 +2892,53 @@
       <c r="V45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2397000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2215000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2174000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2099000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2007000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1931000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2066000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1908000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1717000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1655000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1516000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2162000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2043000</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>16</v>
       </c>
@@ -2855,17 +2957,20 @@
       <c r="V46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="3">
         <v>10000</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>16</v>
       </c>
@@ -2887,8 +2992,8 @@
       <c r="L47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2917,50 +3022,53 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>454000</v>
+      </c>
+      <c r="E48" s="3">
         <v>450000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>505000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>461000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>456000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>454000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>496000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>426000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>422000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>401000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>384000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>354000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>338000</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>16</v>
       </c>
@@ -2979,50 +3087,53 @@
       <c r="V48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9587000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9698000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9809000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9920000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12726000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12837000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12948000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13060000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13171000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13289000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13422000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13553000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13684000</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3041,8 +3152,11 @@
       <c r="V49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,50 +3282,53 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E52" s="3">
         <v>125000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>91000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>123000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>118000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>120000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>67000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>111000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>120000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>117000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>119000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>95000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>97000</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3227,8 +3347,11 @@
       <c r="V52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,50 +3412,53 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12578000</v>
+      </c>
+      <c r="E54" s="3">
         <v>12498000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12579000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12603000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15307000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15342000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15577000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15505000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15430000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15462000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15441000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16164000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>16162000</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3351,8 +3477,11 @@
       <c r="V54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,50 +3529,51 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>199000</v>
+      </c>
+      <c r="E57" s="3">
         <v>150000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>190000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>166000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>171000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>166000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>229000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>221000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>208000</v>
       </c>
       <c r="L57" s="3">
         <v>208000</v>
       </c>
       <c r="M57" s="3">
+        <v>208000</v>
+      </c>
+      <c r="N57" s="3">
         <v>189000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>160000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>138000</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3461,8 +3592,11 @@
       <c r="V57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3470,23 +3604,23 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>13000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>2000</v>
       </c>
       <c r="G58" s="3">
         <v>2000</v>
       </c>
       <c r="H58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I58" s="3">
         <v>4000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -3523,50 +3657,53 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E59" s="3">
         <v>36000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>22000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>52000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>82000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>31000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>38000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>91000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>86000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>116000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>195000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4620000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4592000</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3585,50 +3722,53 @@
       <c r="V59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>347000</v>
+      </c>
+      <c r="E60" s="3">
         <v>290000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>333000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>362000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>346000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>329000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>403000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>391000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>381000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>418000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>384000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4780000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4730000</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3647,41 +3787,44 @@
       <c r="V60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>37000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>51000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>50000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>51000</v>
-      </c>
-      <c r="I61" s="3">
-        <v>39000</v>
       </c>
       <c r="J61" s="3">
         <v>39000</v>
       </c>
       <c r="K61" s="3">
+        <v>39000</v>
+      </c>
+      <c r="L61" s="3">
         <v>42000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>44000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3709,50 +3852,53 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E62" s="3">
         <v>55000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13000</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" s="3">
         <v>7000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>16</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N62" s="3">
         <v>263000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>224000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>233000</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>16</v>
       </c>
@@ -3771,8 +3917,11 @@
       <c r="V62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,50 +4112,53 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>512000</v>
+      </c>
+      <c r="E66" s="3">
         <v>449000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>492000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>525000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>588000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>579000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>653000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>632000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>630000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>675000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>647000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5004000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4963000</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4019,8 +4177,11 @@
       <c r="V66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,50 +4462,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3229000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3162000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3060000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2989000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-274000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-188000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>30000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-33000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-50000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-22000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>57000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11178000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11223000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4353,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,50 +4722,53 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12066000</v>
+      </c>
+      <c r="E76" s="3">
         <v>12049000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12087000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12078000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14719000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14763000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14924000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14873000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14800000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14787000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14794000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11160000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11199000</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4601,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,137 +4852,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45654</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45472</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45381</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45290</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45108</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45017</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44835</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44744</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44653</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44555</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44464</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44373</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44282</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44191</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-102000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-71000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2715000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-86000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-218000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>63000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-28000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-79000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>30000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-45000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-60000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-53000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-26000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-21000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>25000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-14000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,56 +5014,57 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E83" s="3">
         <v>14000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>15000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>9000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>5000</v>
       </c>
       <c r="L83" s="3">
         <v>5000</v>
       </c>
       <c r="M83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="N83" s="3">
         <v>137000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>138000</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R83" s="3">
         <v>526000</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>16</v>
       </c>
@@ -4878,8 +5077,11 @@
       <c r="V83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,56 +5402,59 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>213000</v>
+      </c>
+      <c r="E89" s="3">
         <v>109000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>204000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>126000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>30000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>40000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>109000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>88000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>26000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>171000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>151000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>162000</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R89" s="3">
         <v>599000</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5250,8 +5467,11 @@
       <c r="V89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,8 +5494,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5283,49 +5504,49 @@
         <v>-14000</v>
       </c>
       <c r="E91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-13000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-22000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-24000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-22000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-23000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-17000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-32000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-26000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-32000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-26000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-53000</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>16</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>16</v>
@@ -5336,8 +5557,11 @@
       <c r="V91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,56 +5687,59 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-25000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-22000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-34000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-42000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-22000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-23000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-17000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-32000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>868000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-25000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R94" s="3">
         <v>-157000</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5522,8 +5752,11 @@
       <c r="V94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +5779,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5578,8 +5812,8 @@
       <c r="L96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5608,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,56 +6037,59 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E100" s="3">
         <v>3000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-50000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-71000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-17000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-866000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-36000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R100" s="3">
         <v>91000</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>16</v>
       </c>
@@ -5856,56 +6102,59 @@
       <c r="V100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4000</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="L101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R101" s="3">
         <v>-1000</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>16</v>
       </c>
@@ -5918,56 +6167,59 @@
       <c r="V101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>202000</v>
+      </c>
+      <c r="E102" s="3">
         <v>89000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>132000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>90000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-22000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>19000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>50000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-16000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>138000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>153000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>98000</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R102" s="3">
         <v>532000</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>16</v>
       </c>
@@ -5978,6 +6230,9 @@
         <v>16</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
   <si>
     <t>MBLY</t>
   </si>
@@ -656,313 +656,325 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46018</v>
+      </c>
+      <c r="E7" s="2">
         <v>45927</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45836</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45745</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45654</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45563</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45472</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45381</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45290</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45108</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45017</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44835</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44744</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44653</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44555</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44464</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44373</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44282</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44191</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>446000</v>
+      </c>
+      <c r="E8" s="3">
         <v>504000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>506000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>438000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>490000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>486000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>439000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>239000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>637000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>530000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>454000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>458000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>565000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>450000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>460000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>394000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>356000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>326000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>327000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>377000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>334000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>231000</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>244000</v>
+      </c>
+      <c r="E9" s="3">
         <v>261000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>254000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>231000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>249000</v>
       </c>
       <c r="H9" s="3">
         <v>249000</v>
       </c>
       <c r="I9" s="3">
+        <v>249000</v>
+      </c>
+      <c r="J9" s="3">
         <v>230000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>185000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>293000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>258000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>230000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>251000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>265000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>233000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>231000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>218000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>202000</v>
-      </c>
-      <c r="T9" s="3">
-        <v>173000</v>
       </c>
       <c r="U9" s="3">
         <v>173000</v>
       </c>
       <c r="V9" s="3">
+        <v>173000</v>
+      </c>
+      <c r="W9" s="3">
         <v>183000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>176000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>155000</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>202000</v>
+      </c>
+      <c r="E10" s="3">
         <v>243000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>252000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>207000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>241000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>237000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>209000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>54000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>344000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>272000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>224000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>207000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>300000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>217000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>229000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>176000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>154000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>153000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>154000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>194000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>158000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>76000</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -987,76 +999,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>290000</v>
+      </c>
+      <c r="E12" s="3">
         <v>304000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>282000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>275000</v>
       </c>
-      <c r="G12" s="3">
-        <v>276400</v>
-      </c>
       <c r="H12" s="3">
+        <v>281000</v>
+      </c>
+      <c r="I12" s="3">
         <v>303000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>256000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>243000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>225000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>218000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>211000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>235000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>224000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>206000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>179000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>180000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>154000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>132000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>128000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>130000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>128000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1123,8 +1139,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1137,15 +1156,15 @@
       <c r="F14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="3">
-        <v>4600</v>
+      <c r="G14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>2695000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1161,8 +1180,8 @@
       <c r="N14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1191,8 +1210,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1206,7 +1228,7 @@
         <v>35000</v>
       </c>
       <c r="G15" s="3">
-        <v>33000</v>
+        <v>35000</v>
       </c>
       <c r="H15" s="3">
         <v>33000</v>
@@ -1215,29 +1237,29 @@
         <v>33000</v>
       </c>
       <c r="J15" s="3">
+        <v>33000</v>
+      </c>
+      <c r="K15" s="3">
         <v>31000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>32000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>26000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>25000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>24000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>17000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>16000</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1247,8 +1269,8 @@
       <c r="T15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1259,8 +1281,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1282,144 +1307,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>586000</v>
+      </c>
+      <c r="E17" s="3">
         <v>613000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>580000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>555000</v>
       </c>
-      <c r="G17" s="3">
-        <v>571400</v>
-      </c>
       <c r="H17" s="3">
+        <v>576000</v>
+      </c>
+      <c r="I17" s="3">
         <v>598000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>533000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>477000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>564000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>522000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>487000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>539000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>541000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>475000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>450000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>440000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>400000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>346000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>342000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>355000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>345000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>308000</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-140000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-109000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-74000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-117000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-81400</v>
-      </c>
       <c r="H18" s="3">
+        <v>-86000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-112000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-94000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-238000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>73000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-33000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-81000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>24000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-46000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-44000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-20000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-15000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>22000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-11000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-77000</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1444,144 +1476,151 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="3">
-        <v>-13000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-18000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-18000</v>
+      <c r="E20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I20" s="3">
-        <v>-13000</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" s="3">
         <v>-17000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-11000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-15000</v>
       </c>
       <c r="M20" s="3">
         <v>-15000</v>
       </c>
       <c r="N20" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="O20" s="3">
         <v>-8000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>14000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2000</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>2000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-74000</v>
       </c>
-      <c r="E21" s="3">
-        <v>-26000</v>
-      </c>
       <c r="F21" s="3">
-        <v>-64000</v>
+        <v>-39000</v>
       </c>
       <c r="G21" s="3">
-        <v>-30400</v>
+        <v>-82000</v>
       </c>
       <c r="H21" s="3">
+        <v>-53000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-79000</v>
       </c>
-      <c r="I21" s="3">
-        <v>-48000</v>
-      </c>
       <c r="J21" s="3">
+        <v>-61000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-190000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>116000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>49000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-49000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>175000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>119000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T21" s="3">
         <v>480000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V21" s="3">
         <v>237000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1618,15 +1657,15 @@
       <c r="N22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P22" s="3">
         <v>4000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11000</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>16</v>
       </c>
@@ -1642,150 +1681,159 @@
       <c r="V22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-125000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-92000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-61000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-99000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-68000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2793000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-81000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-221000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>84000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>23000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-73000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>34000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-44000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-46000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-20000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-15000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>24000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-16000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E24" s="3">
         <v>4000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>3000</v>
       </c>
       <c r="G24" s="3">
         <v>3000</v>
       </c>
       <c r="H24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I24" s="3">
         <v>-78000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-3000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>21000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>10000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4000</v>
-      </c>
-      <c r="P24" s="3">
-        <v>15000</v>
       </c>
       <c r="Q24" s="3">
         <v>15000</v>
       </c>
       <c r="R24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S24" s="3">
         <v>16000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7000</v>
-      </c>
-      <c r="T24" s="3">
-        <v>6000</v>
       </c>
       <c r="U24" s="3">
         <v>6000</v>
       </c>
       <c r="V24" s="3">
+        <v>6000</v>
+      </c>
+      <c r="W24" s="3">
         <v>-1000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-2000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1852,144 +1900,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-127000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-96000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-67000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-102000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-71000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2715000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-86000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-218000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>63000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>17000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-28000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-79000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>30000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-45000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-60000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-53000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-26000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-21000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>25000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-14000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-127000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-96000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-67000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-102000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-71000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2715000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-86000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-218000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>63000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>17000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-28000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-79000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>30000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-45000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-60000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-53000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-26000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-21000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>25000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-14000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2056,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2124,8 +2184,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2192,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2260,144 +2326,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E32" s="3">
-        <v>13000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>18000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>18000</v>
+      <c r="E32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I32" s="3">
-        <v>13000</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K32" s="3">
         <v>17000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>11000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>15000</v>
       </c>
       <c r="M32" s="3">
         <v>15000</v>
       </c>
       <c r="N32" s="3">
+        <v>15000</v>
+      </c>
+      <c r="O32" s="3">
         <v>8000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-14000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2000</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-2000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-127000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-96000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-67000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-102000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-71000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2715000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-86000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-218000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>63000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-28000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-79000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>30000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-45000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-60000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-53000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-26000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-21000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>25000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-14000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2464,149 +2539,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-127000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-96000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-67000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-102000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-71000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2715000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-86000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-218000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>63000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-28000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-79000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>30000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-45000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-60000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-53000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-26000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-21000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>25000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-14000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46018</v>
+      </c>
+      <c r="E38" s="2">
         <v>45927</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45836</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45745</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45654</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45563</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45472</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45381</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45290</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45108</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45017</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44835</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44744</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44653</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44555</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44464</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44373</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44282</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44191</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2631,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2657,56 +2742,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1836000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1749000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1709000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1512000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1426000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1293000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1203000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1223000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1212000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1193000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1142000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1161000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1024000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>871000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>774000</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2725,8 +2811,11 @@
       <c r="X41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2737,17 +2826,17 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>44000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>10000</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -2793,56 +2882,59 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E43" s="3">
         <v>201000</v>
-      </c>
-      <c r="E43" s="3">
-        <v>217000</v>
       </c>
       <c r="F43" s="3">
         <v>217000</v>
       </c>
       <c r="G43" s="3">
+        <v>217000</v>
+      </c>
+      <c r="H43" s="3">
         <v>212000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>223000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>204000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>120000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>357000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>281000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>240000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>239000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>269000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1123000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1115000</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2861,56 +2953,59 @@
       <c r="X43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>327000</v>
+      </c>
+      <c r="E44" s="3">
         <v>318000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>325000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>364000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>415000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>457000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>485000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>456000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>391000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>354000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>263000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>173000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>113000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>105000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>98000</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>16</v>
       </c>
@@ -2929,56 +3024,59 @@
       <c r="X44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>184000</v>
+      </c>
+      <c r="E45" s="3">
         <v>148000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>146000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>78000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>121000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>116000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>115000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>132000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>106000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>80000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>72000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>82000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>110000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>63000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>56000</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2997,56 +3095,59 @@
       <c r="X45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2478000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2416000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2397000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2215000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2174000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2099000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2007000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1931000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2066000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1908000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1717000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1655000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1516000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2162000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2043000</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3065,8 +3166,11 @@
       <c r="X46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3076,12 +3180,12 @@
       <c r="E47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="3">
         <v>10000</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3103,8 +3207,8 @@
       <c r="N47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3133,56 +3237,59 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>523000</v>
+      </c>
+      <c r="E48" s="3">
         <v>453000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>454000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>450000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>505000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>461000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>456000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>454000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>496000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>426000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>422000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>401000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>384000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>354000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>338000</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3201,56 +3308,59 @@
       <c r="X48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9366000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9476000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9587000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9698000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9809000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9920000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12726000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12837000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12948000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13060000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13171000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13289000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13422000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13553000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>13684000</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3269,8 +3379,11 @@
       <c r="X49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3337,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3405,56 +3521,59 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E52" s="3">
         <v>135000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>140000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>125000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>91000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>123000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>118000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>120000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>67000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>111000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>120000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>117000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>119000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>95000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>97000</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3473,8 +3592,11 @@
       <c r="X52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3541,56 +3663,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12492000</v>
+      </c>
+      <c r="E54" s="3">
         <v>12480000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12578000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12498000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12579000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12603000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15307000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15342000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15577000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15505000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15430000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15462000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15441000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16164000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16162000</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3609,8 +3734,11 @@
       <c r="X54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3635,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3661,56 +3790,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>228000</v>
+      </c>
+      <c r="E57" s="3">
         <v>211000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>199000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>150000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>190000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>166000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>171000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>166000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>229000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>221000</v>
-      </c>
-      <c r="M57" s="3">
-        <v>208000</v>
       </c>
       <c r="N57" s="3">
         <v>208000</v>
       </c>
       <c r="O57" s="3">
+        <v>208000</v>
+      </c>
+      <c r="P57" s="3">
         <v>189000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>160000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>138000</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3729,13 +3859,16 @@
       <c r="X57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -3744,23 +3877,23 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>13000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>2000</v>
       </c>
       <c r="I58" s="3">
         <v>2000</v>
       </c>
       <c r="J58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K58" s="3">
         <v>4000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3797,56 +3930,59 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E59" s="3">
         <v>38000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>33000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>36000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>22000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>52000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>82000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>31000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>38000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>91000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>86000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>116000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>195000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4620000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4592000</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3865,56 +4001,59 @@
       <c r="X59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>406000</v>
+      </c>
+      <c r="E60" s="3">
         <v>374000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>347000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>290000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>333000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>362000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>346000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>329000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>403000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>391000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>381000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>418000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>384000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4780000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4730000</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3933,47 +4072,50 @@
       <c r="X60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E61" s="3">
         <v>61000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>56000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>53000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>37000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>51000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>50000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>51000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>39000</v>
       </c>
       <c r="L61" s="3">
         <v>39000</v>
       </c>
       <c r="M61" s="3">
+        <v>39000</v>
+      </c>
+      <c r="N61" s="3">
         <v>42000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>44000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4001,56 +4143,59 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4000</v>
+        <v>23000</v>
       </c>
       <c r="E62" s="3">
         <v>4000</v>
       </c>
       <c r="F62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G62" s="3">
         <v>2000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13000</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>16</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L62" s="3">
         <v>7000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P62" s="3">
         <v>263000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>224000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>233000</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4069,8 +4214,11 @@
       <c r="X62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4137,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4205,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4273,56 +4427,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>611000</v>
+      </c>
+      <c r="E66" s="3">
         <v>545000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>512000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>449000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>492000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>525000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>588000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>579000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>653000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>632000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>630000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>675000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>647000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5004000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4963000</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4341,8 +4498,11 @@
       <c r="X66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4367,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4435,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4503,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4571,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4639,56 +4809,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3452000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3325000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3229000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3162000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3060000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2989000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-274000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-188000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>30000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-33000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-50000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-22000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>57000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>11178000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>11223000</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4707,8 +4880,11 @@
       <c r="X72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4775,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4843,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4911,56 +5093,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11881000</v>
+      </c>
+      <c r="E76" s="3">
         <v>11935000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12066000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12049000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12087000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12078000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14719000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14763000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14924000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14873000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14800000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14787000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14794000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11160000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11199000</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4979,8 +5164,11 @@
       <c r="X76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5047,149 +5235,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46018</v>
+      </c>
+      <c r="E80" s="2">
         <v>45927</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45836</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45745</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45654</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45563</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45472</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45381</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45290</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45108</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45017</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44835</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44744</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44653</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44555</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44464</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44373</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44282</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44191</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-127000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-96000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-67000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-102000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-71000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2715000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-86000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-218000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>63000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-28000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-79000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>30000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-45000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-60000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-53000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-26000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-21000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>25000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-14000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5214,8 +5411,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5226,50 +5424,50 @@
         <v>16000</v>
       </c>
       <c r="F83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="G83" s="3">
         <v>14000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>15000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>5000</v>
       </c>
       <c r="N83" s="3">
         <v>5000</v>
       </c>
       <c r="O83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="P83" s="3">
         <v>137000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>138000</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T83" s="3">
         <v>526000</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5282,8 +5480,11 @@
       <c r="X83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5350,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5418,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5486,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5554,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5622,62 +5835,65 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>113000</v>
+      </c>
+      <c r="E89" s="3">
         <v>167000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>213000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>109000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>204000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>126000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>30000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>40000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>109000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>88000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>26000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>171000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>151000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>162000</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T89" s="3">
         <v>599000</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5690,8 +5906,11 @@
       <c r="X89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5716,64 +5935,65 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-24000</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-14000</v>
       </c>
       <c r="F91" s="3">
         <v>-14000</v>
       </c>
       <c r="G91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="H91" s="3">
         <v>-13000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-22000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-24000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-22000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-23000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-32000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-26000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-32000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-53000</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>16</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>16</v>
@@ -5784,8 +6004,11 @@
       <c r="X91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5852,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5920,62 +6146,65 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-25000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-25000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-22000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-34000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-42000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-22000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-23000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-17000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-32000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-26000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>868000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T94" s="3">
         <v>-157000</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5988,8 +6217,11 @@
       <c r="X94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6014,8 +6246,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6052,8 +6285,8 @@
       <c r="N96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6082,8 +6315,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6150,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6218,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6286,62 +6528,65 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-102000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-50000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-71000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-17000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-866000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-36000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T100" s="3">
         <v>91000</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6354,62 +6599,65 @@
       <c r="X100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>3000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4000</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="M101" s="3">
         <v>-3000</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="N101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T101" s="3">
         <v>-1000</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>16</v>
       </c>
@@ -6422,62 +6670,65 @@
       <c r="X101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E102" s="3">
         <v>40000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>202000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>89000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>132000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>90000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-22000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>12000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>19000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>50000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-16000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>138000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>153000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>98000</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T102" s="3">
         <v>532000</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6488,6 +6739,9 @@
         <v>16</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
   <si>
     <t>MBLY</t>
   </si>
@@ -656,325 +656,338 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E7" s="2">
         <v>46018</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45927</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45836</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45745</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45654</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45563</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45472</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45381</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45290</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45108</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45017</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44835</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44744</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44653</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44555</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44464</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44373</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44282</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44191</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>558000</v>
+      </c>
+      <c r="E8" s="3">
         <v>446000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>504000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>506000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>438000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>490000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>486000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>439000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>239000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>637000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>530000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>454000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>458000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>565000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>450000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>460000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>394000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>356000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>326000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>327000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>377000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>334000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>231000</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>283000</v>
+      </c>
+      <c r="E9" s="3">
         <v>244000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>261000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>254000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>231000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>249000</v>
       </c>
       <c r="I9" s="3">
         <v>249000</v>
       </c>
       <c r="J9" s="3">
+        <v>249000</v>
+      </c>
+      <c r="K9" s="3">
         <v>230000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>185000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>293000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>258000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>230000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>251000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>265000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>233000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>231000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>218000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>202000</v>
-      </c>
-      <c r="U9" s="3">
-        <v>173000</v>
       </c>
       <c r="V9" s="3">
         <v>173000</v>
       </c>
       <c r="W9" s="3">
+        <v>173000</v>
+      </c>
+      <c r="X9" s="3">
         <v>183000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>176000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>155000</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>275000</v>
+      </c>
+      <c r="E10" s="3">
         <v>202000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>243000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>252000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>207000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>241000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>237000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>209000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>54000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>344000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>272000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>224000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>207000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>300000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>217000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>229000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>176000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>154000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>153000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>154000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>194000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>158000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>76000</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1000,79 +1013,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>323000</v>
+      </c>
+      <c r="E12" s="3">
         <v>290000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>304000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>282000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>275000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>281000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>303000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>256000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>243000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>225000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>218000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>211000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>235000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>224000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>206000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>179000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>180000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>154000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>132000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>128000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>130000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>128000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1142,13 +1159,16 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>16</v>
+      <c r="D14" s="3">
+        <v>3788000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>16</v>
@@ -1159,15 +1179,15 @@
       <c r="G14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>2695000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1183,8 +1203,8 @@
       <c r="O14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1213,13 +1233,16 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>35000</v>
+        <v>38000</v>
       </c>
       <c r="E15" s="3">
         <v>35000</v>
@@ -1231,7 +1254,7 @@
         <v>35000</v>
       </c>
       <c r="H15" s="3">
-        <v>33000</v>
+        <v>35000</v>
       </c>
       <c r="I15" s="3">
         <v>33000</v>
@@ -1240,29 +1263,29 @@
         <v>33000</v>
       </c>
       <c r="K15" s="3">
+        <v>33000</v>
+      </c>
+      <c r="L15" s="3">
         <v>31000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>32000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>26000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>25000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>24000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>17000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>16000</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1272,8 +1295,8 @@
       <c r="U15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1284,8 +1307,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,150 +1334,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>666000</v>
+      </c>
+      <c r="E17" s="3">
         <v>586000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>613000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>580000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>555000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>576000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>598000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>533000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>477000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>564000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>522000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>487000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>539000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>541000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>475000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>450000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>440000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>400000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>346000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>342000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>355000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>345000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>308000</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-108000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-140000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-109000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-74000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-117000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-86000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-112000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-94000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-238000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>73000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-33000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-81000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>24000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-25000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-46000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-44000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-20000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-15000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>22000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-77000</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1477,8 +1510,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1503,124 +1537,130 @@
       <c r="J20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L20" s="3">
         <v>-17000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-11000</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-15000</v>
       </c>
       <c r="N20" s="3">
         <v>-15000</v>
       </c>
       <c r="O20" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="P20" s="3">
         <v>-8000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>14000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2000</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>2000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-70000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-105000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-74000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-39000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-82000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-53000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-79000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-61000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-190000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>116000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>49000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-49000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>175000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>119000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U21" s="3">
         <v>480000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W21" s="3">
         <v>237000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1660,15 +1700,15 @@
       <c r="O22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q22" s="3">
         <v>4000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>11000</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>16</v>
       </c>
@@ -1684,156 +1724,165 @@
       <c r="W22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3882000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-125000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-92000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-61000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-99000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-68000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2793000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-81000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-221000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>84000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>23000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-18000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-73000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>34000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-30000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>8000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-44000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-46000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-20000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-15000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>24000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-64000</v>
+      </c>
+      <c r="E24" s="3">
         <v>2000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>3000</v>
       </c>
       <c r="H24" s="3">
         <v>3000</v>
       </c>
       <c r="I24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J24" s="3">
         <v>-78000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>21000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4000</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>15000</v>
       </c>
       <c r="R24" s="3">
         <v>15000</v>
       </c>
       <c r="S24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="T24" s="3">
         <v>16000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7000</v>
-      </c>
-      <c r="U24" s="3">
-        <v>6000</v>
       </c>
       <c r="V24" s="3">
         <v>6000</v>
       </c>
       <c r="W24" s="3">
+        <v>6000</v>
+      </c>
+      <c r="X24" s="3">
         <v>-1000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,150 +1952,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3818000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-127000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-96000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-67000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-102000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-71000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2715000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-86000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-218000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>63000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>17000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-28000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-79000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>30000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-45000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-60000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-53000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-26000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-21000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>25000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3818000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-127000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-96000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-67000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-102000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-71000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2715000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-86000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-218000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>63000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>17000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-28000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-79000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>30000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-45000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-60000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-53000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-26000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-21000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>25000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,8 +2396,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2355,124 +2425,130 @@
       <c r="J32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L32" s="3">
         <v>17000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>11000</v>
-      </c>
-      <c r="M32" s="3">
-        <v>15000</v>
       </c>
       <c r="N32" s="3">
         <v>15000</v>
       </c>
       <c r="O32" s="3">
+        <v>15000</v>
+      </c>
+      <c r="P32" s="3">
         <v>8000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2000</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-2000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>5000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3818000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-127000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-96000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-67000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-102000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-71000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2715000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-86000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-218000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>63000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>17000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-28000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-79000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>30000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-45000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-60000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-53000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-26000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-21000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>25000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,155 +2618,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3818000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-127000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-96000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-67000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-102000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-71000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2715000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-86000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-218000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>63000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>17000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-28000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-79000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>30000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-45000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-60000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-53000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-26000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-21000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>25000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E38" s="2">
         <v>46018</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45927</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45836</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45745</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45654</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45563</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45472</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45381</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45290</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45108</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45017</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44835</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44744</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44653</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44555</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44464</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44373</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44282</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44191</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,59 +2829,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1211000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1836000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1749000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1709000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1512000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1426000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1293000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1203000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1223000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1212000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1193000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1142000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1161000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1024000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>871000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>774000</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2814,13 +2901,16 @@
       <c r="Y41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>133000</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -2829,17 +2919,17 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>44000</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>10000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -2885,59 +2975,62 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>226000</v>
+      </c>
+      <c r="E43" s="3">
         <v>131000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>201000</v>
-      </c>
-      <c r="F43" s="3">
-        <v>217000</v>
       </c>
       <c r="G43" s="3">
         <v>217000</v>
       </c>
       <c r="H43" s="3">
+        <v>217000</v>
+      </c>
+      <c r="I43" s="3">
         <v>212000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>223000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>204000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>120000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>357000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>281000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>240000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>239000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>269000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1123000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1115000</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2956,59 +3049,62 @@
       <c r="Y43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>303000</v>
+      </c>
+      <c r="E44" s="3">
         <v>327000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>318000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>325000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>364000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>415000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>457000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>485000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>456000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>391000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>354000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>263000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>173000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>113000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>105000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>98000</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3027,59 +3123,62 @@
       <c r="Y44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E45" s="3">
         <v>184000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>148000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>146000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>78000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>121000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>116000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>115000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>132000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>106000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>80000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>72000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>82000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>110000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>63000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>56000</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3098,59 +3197,62 @@
       <c r="Y45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1993000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2478000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2416000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2397000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2215000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2174000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2099000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2007000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1931000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2066000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1908000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1717000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1655000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1516000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2162000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2043000</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3169,8 +3271,11 @@
       <c r="Y46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3183,12 +3288,12 @@
       <c r="F47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H47" s="3">
         <v>10000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3210,8 +3315,8 @@
       <c r="O47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3240,59 +3345,62 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>468000</v>
+      </c>
+      <c r="E48" s="3">
         <v>523000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>453000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>454000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>450000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>505000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>461000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>456000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>454000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>496000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>426000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>422000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>401000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>384000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>354000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>338000</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3311,59 +3419,62 @@
       <c r="Y48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6092000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9366000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9476000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9587000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9698000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9809000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9920000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12726000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12837000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12948000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13060000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13171000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13289000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13422000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>13553000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>13684000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3382,8 +3493,11 @@
       <c r="Y49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,59 +3641,62 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E52" s="3">
         <v>125000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>135000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>140000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>125000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>91000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>123000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>118000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>120000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>67000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>111000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>120000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>117000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>119000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>95000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>97000</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3595,8 +3715,11 @@
       <c r="Y52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,59 +3789,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8735000</v>
+      </c>
+      <c r="E54" s="3">
         <v>12492000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12480000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12578000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12498000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12579000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12603000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15307000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15342000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15577000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15505000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15430000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15462000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15441000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16164000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16162000</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3737,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,8 +3921,9 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3800,50 +3931,50 @@
         <v>228000</v>
       </c>
       <c r="E57" s="3">
+        <v>228000</v>
+      </c>
+      <c r="F57" s="3">
         <v>211000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>199000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>150000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>190000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>166000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>171000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>166000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>229000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>221000</v>
-      </c>
-      <c r="N57" s="3">
-        <v>208000</v>
       </c>
       <c r="O57" s="3">
         <v>208000</v>
       </c>
       <c r="P57" s="3">
+        <v>208000</v>
+      </c>
+      <c r="Q57" s="3">
         <v>189000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>160000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>138000</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3862,17 +3993,20 @@
       <c r="Y57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>18000</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
@@ -3880,23 +4014,23 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>13000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>2000</v>
       </c>
       <c r="J58" s="3">
         <v>2000</v>
       </c>
       <c r="K58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L58" s="3">
         <v>4000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -3933,59 +4067,62 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E59" s="3">
         <v>19000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>38000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>33000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>36000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>52000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>82000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>31000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>38000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>91000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>86000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>116000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>195000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4620000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4592000</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4004,59 +4141,62 @@
       <c r="Y59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>419000</v>
+      </c>
+      <c r="E60" s="3">
         <v>406000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>374000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>347000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>290000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>333000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>362000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>346000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>329000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>403000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>391000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>381000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>418000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>384000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4780000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4730000</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4075,50 +4215,53 @@
       <c r="Y60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E61" s="3">
         <v>44000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>61000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>56000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>53000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>37000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>51000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>50000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>51000</v>
-      </c>
-      <c r="L61" s="3">
-        <v>39000</v>
       </c>
       <c r="M61" s="3">
         <v>39000</v>
       </c>
       <c r="N61" s="3">
+        <v>39000</v>
+      </c>
+      <c r="O61" s="3">
         <v>42000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>44000</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4146,59 +4289,62 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E62" s="3">
         <v>23000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>4000</v>
       </c>
       <c r="F62" s="3">
         <v>4000</v>
       </c>
       <c r="G62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H62" s="3">
         <v>2000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13000</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>16</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M62" s="3">
         <v>7000</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>16</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q62" s="3">
         <v>263000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>224000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>233000</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4217,8 +4363,11 @@
       <c r="Y62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,59 +4585,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>571000</v>
+      </c>
+      <c r="E66" s="3">
         <v>611000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>545000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>512000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>449000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>492000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>525000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>588000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>579000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>653000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>632000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>630000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>675000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>647000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5004000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4963000</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4501,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4741,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,59 +4983,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-7270000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3452000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3325000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3229000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3162000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3060000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2989000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-274000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-188000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>30000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-33000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-50000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-22000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>57000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>11178000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>11223000</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4883,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,59 +5279,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8164000</v>
+      </c>
+      <c r="E76" s="3">
         <v>11881000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11935000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12066000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12049000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12087000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12078000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14719000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14763000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14924000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14873000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14800000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14787000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14794000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11160000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11199000</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5167,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,155 +5427,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E80" s="2">
         <v>46018</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45927</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45836</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45745</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45654</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45563</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45472</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45381</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45290</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45108</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45017</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44835</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44744</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44653</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44555</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44464</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44373</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44282</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44191</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3818000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-127000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-96000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-67000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-102000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-71000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2715000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-86000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-218000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>63000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>17000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-28000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-79000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>30000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-45000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-60000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-53000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-26000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-21000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>25000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,13 +5610,14 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="E83" s="3">
         <v>16000</v>
@@ -5427,50 +5626,50 @@
         <v>16000</v>
       </c>
       <c r="G83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="H83" s="3">
         <v>14000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>15000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>5000</v>
       </c>
       <c r="O83" s="3">
         <v>5000</v>
       </c>
       <c r="P83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>137000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>138000</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U83" s="3">
         <v>526000</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5483,8 +5682,11 @@
       <c r="Y83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,65 +6052,68 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E89" s="3">
         <v>113000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>167000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>213000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>109000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>204000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>126000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>30000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>40000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>109000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>88000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>26000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>171000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>151000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>162000</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U89" s="3">
         <v>599000</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5909,8 +6126,11 @@
       <c r="Y89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,67 +6156,68 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-27000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-24000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-14000</v>
       </c>
       <c r="G91" s="3">
         <v>-14000</v>
       </c>
       <c r="H91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-13000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-22000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-24000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-22000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-23000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-17000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-32000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-26000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-32000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-26000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-53000</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>16</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>16</v>
@@ -6007,8 +6228,11 @@
       <c r="Y91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,65 +6376,68 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-699000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-27000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-25000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-14000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-25000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-22000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-34000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-42000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-23000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-17000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-32000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-26000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>868000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-25000</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T94" s="3">
+      <c r="T94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U94" s="3">
         <v>-157000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6220,8 +6450,11 @@
       <c r="Y94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6288,8 +6522,8 @@
       <c r="O96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6318,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,65 +6774,68 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-102000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-50000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-71000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-17000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-9000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-866000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-36000</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U100" s="3">
         <v>91000</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6602,65 +6848,68 @@
       <c r="Y100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4000</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="N101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-3000</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T101" s="3">
+      <c r="T101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U101" s="3">
         <v>-1000</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>16</v>
       </c>
@@ -6673,65 +6922,68 @@
       <c r="Y101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-622000</v>
+      </c>
+      <c r="E102" s="3">
         <v>91000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>40000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>202000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>89000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>132000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>90000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-22000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>12000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>19000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>50000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-16000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>138000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>153000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>98000</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U102" s="3">
         <v>532000</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6742,6 +6994,9 @@
         <v>16</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>16</v>
       </c>
     </row>
